--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_decimal_place_correction.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n">
-        <v>25.1</v>
+        <v>2.5</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>13.6</v>
@@ -746,7 +746,7 @@
         <v>19.3</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>19.5</v>
+        <v>1.5</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>13.1</v>
@@ -758,10 +758,10 @@
         <v>4.7</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.2</v>
+        <v>28.6</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>14.7</v>
+        <v>14.2</v>
       </c>
       <c r="M4" s="3" t="n"/>
       <c r="N4" s="3" t="n">
@@ -770,35 +770,39 @@
       <c r="O4" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="P4" s="3" t="n"/>
-      <c r="Q4" s="3" t="n">
-        <v>25</v>
+      <c r="P4" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>15</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>16.5</v>
+        <v>1.5</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>52</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>15.2</v>
+        <v>18.2</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>18</v>
+        <v>1.6</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z4" s="3" t="n"/>
+        <v>5.5</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -812,7 +816,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
+      <c r="C5" s="3" t="n">
+        <v>508.2</v>
+      </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n">
         <v>14.2</v>
@@ -821,34 +827,34 @@
         <v>19.1</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>12.9</v>
+        <v>2.7</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>15.7</v>
+        <v>1.7</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="M5" s="8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="M5" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>18.9</v>
+        <v>6.1</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1092</v>
+        <v>92.8</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>22.4</v>
@@ -857,10 +863,10 @@
         <v>17.2</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>16.7</v>
+        <v>17.6</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>61.9</v>
+        <v>61.5</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>10.4</v>
@@ -872,11 +878,13 @@
         <v>16.8</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="Y5" s="3" t="n"/>
+        <v>18.3</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>27</v>
+      </c>
       <c r="Z5" s="3" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -892,61 +900,59 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>508.9</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>24.1</v>
+        <v>52.9</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>244.1</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="H6" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>10</v>
+        <v>20.6</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>43.8</v>
+        <v>41.8</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="N6" s="8" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="N6" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="O6" s="3" t="n">
-        <v>192.8</v>
-      </c>
+      <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="n">
-        <v>1.2</v>
+        <v>21.2</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>145.8</v>
+        <v>43.6</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>17.9</v>
+        <v>13.5</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>59.1</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>18.7</v>
@@ -955,13 +961,13 @@
         <v>16.6</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>18.3</v>
+        <v>1.7</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>87</v>
+        <v>82.5</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -977,76 +983,76 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>512.9</v>
+        <v>22.8</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>13.2</v>
+        <v>15.8</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>10.7</v>
+        <v>10.2</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>3.4</v>
+        <v>23.4</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>8</v>
+        <v>1.2</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="M7" s="8" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M7" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="N7" s="3" t="n">
-        <v>16.2</v>
+      <c r="N7" s="8" t="n">
+        <v>83.7</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P7" s="8" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="Q7" s="8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>17.6</v>
+        <v>718.1</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="R7" s="8" t="n">
+        <v>77.59999999999999</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>17.4</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>64</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="W7" s="8" t="n">
+      <c r="W7" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>17.7</v>
+        <v>1.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>82.8</v>
+        <v>20.8</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1062,7 +1068,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>229.8</v>
+        <v>24.9</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>21.5</v>
@@ -1071,52 +1077,50 @@
         <v>15.8</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>17.7</v>
+        <v>12.7</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12.9</v>
+        <v>1.9</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>13.1</v>
+        <v>15.1</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N8" s="8" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>195.9</v>
-      </c>
+        <v>14.6</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O8" s="3" t="n"/>
       <c r="P8" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="Q8" s="8" t="n">
-        <v>120.5</v>
+        <v>11.8</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>20.5</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>17.1</v>
@@ -1124,14 +1128,14 @@
       <c r="W8" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="X8" s="8" t="n">
-        <v>17.8</v>
+      <c r="X8" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>80.8</v>
+        <v>90</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1147,72 +1151,78 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.5</v>
+        <v>445</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>18.5</v>
+        <v>1183.5</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>615.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G9" s="3" t="n"/>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>9.1</v>
+      </c>
       <c r="H9" s="3" t="n">
-        <v>63.4</v>
+        <v>63.1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>10.8</v>
+        <v>206.1</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>264.4</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>51.1</v>
+        <v>16.4</v>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17179190
+1
+</t>
+        </is>
       </c>
       <c r="L9" s="3" t="n"/>
       <c r="M9" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>45.9</v>
+        <v>18.8</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>6.6</v>
+        <v>0.7</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>114</v>
+        <v>173.8</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>26.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>13.6</v>
+        <v>7.6</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>5301</v>
+        <v>3</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>194</v>
+        <v>40.1</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>16</v>
+        <v>82.8</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>17.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>90</v>
+        <v>45.1</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>2</v>
+        <v>19.4</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1228,7 +1238,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>445</v>
+        <v>194.8</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>23.7</v>
@@ -1237,21 +1247,23 @@
         <v>13.5</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>10.2</v>
+        <v>1.2</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K10" s="3" t="n"/>
+      <c r="K10" s="3" t="n">
+        <v>10.2</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>14.7</v>
       </c>
@@ -1259,28 +1271,28 @@
         <v>13.8</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>15.8</v>
+        <v>0.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>21.8</v>
+        <v>880.1</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>17.6</v>
+        <v>7.6</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>17.2</v>
+        <v>7.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>62.5</v>
+        <v>62.8</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>10.6</v>
+        <v>1.6</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>18.8</v>
@@ -1289,13 +1301,13 @@
         <v>16.8</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>89.7</v>
+        <v>1.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>1088.4</v>
+        <v>83</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1311,10 +1323,10 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>154.8</v>
+        <v>298.9</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>22.5</v>
+        <v>2.5</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>13.7</v>
@@ -1323,64 +1335,68 @@
         <v>18.1</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>33.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>148.1</v>
+        <v>0.8</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>1.1</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>10.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>14.8</v>
+        <v>28.2</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>468.6</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>19</v>
+        <v>12.5</v>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+198
+</t>
+        </is>
       </c>
       <c r="T11" s="3" t="n">
-        <v>85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="W11" s="8" t="n">
-        <v>63.8</v>
+        <v>3.4</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>13.7</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>17.9</v>
+        <v>1.8</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1396,61 +1412,61 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>229.5</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>22.4</v>
+        <v>298.9</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>2.9</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>13.3</v>
+        <v>18.5</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="G12" s="8" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="H12" s="8" t="n">
+      <c r="G12" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H12" s="3" t="n">
         <v>13</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1</v>
+        <v>11.2</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>13.9</v>
+        <v>14.8</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>13.7</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>18</v>
+        <v>10.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>92</v>
+        <v>94.5</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>1.2</v>
+        <v>12.4</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="R12" s="8" t="n">
-        <v>17.1</v>
+        <v>20.3</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>74.5</v>
+        <v>4.5</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>16.2</v>
+        <v>6.4</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>16.5</v>
@@ -1459,13 +1475,13 @@
         <v>14.8</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>17.8</v>
+        <v>1.5</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>40.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1481,10 +1497,10 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>29322</v>
+        <v>32.4</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>23.6</v>
+        <v>63.6</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>13.8</v>
@@ -1493,16 +1509,16 @@
         <v>18.7</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>19.8</v>
+        <v>49.8</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="K13" s="3" t="n"/>
       <c r="L13" s="3" t="n">
@@ -1512,43 +1528,41 @@
         <v>14.4</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="O13" s="3" t="n">
-        <v>946.4</v>
-      </c>
-      <c r="P13" s="8" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Q13" s="3" t="n">
-        <v>15.8</v>
+        <v>1.1</v>
+      </c>
+      <c r="O13" s="3" t="n"/>
+      <c r="P13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="8" t="n">
+        <v>58.2</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="S13" s="3" t="n">
-        <v>16.8</v>
+      <c r="S13" s="8" t="n">
+        <v>68.5</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="W13" s="8" t="n">
+      <c r="W13" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>15.9</v>
+        <v>1.4</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>85</v>
+        <v>92.8</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>12.8</v>
+        <v>1.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1563,58 +1577,60 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>324</v>
-      </c>
+      <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>13.4</v>
+        <v>1.4</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="K14" s="3" t="n"/>
+      <c r="K14" s="3" t="n">
+        <v>5.3</v>
+      </c>
       <c r="L14" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="N14" s="8" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="O14" s="3" t="n"/>
-      <c r="P14" s="8" t="n">
-        <v>11</v>
+      <c r="N14" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>21.5</v>
+        <v>41.3</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="S14" s="8" t="n">
+      <c r="S14" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>171.9</v>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v>71.2</v>
+        <v>28.8</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>2.1</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>18.2</v>
@@ -1623,13 +1639,13 @@
         <v>16.6</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>17.4</v>
+        <v>18</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>92</v>
+        <v>8.5</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>11.6</v>
+        <v>2.8</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1645,44 +1661,42 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>307.9</v>
+        <v>1475.5</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F15" s="3" t="n"/>
+        <v>45.1</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="G15" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H15" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H15" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="I15" s="3" t="n">
-        <v>15.4</v>
+      <c r="I15" s="8" t="n">
+        <v>12.1</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="M15" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="M15" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="N15" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="O15" s="3" t="n">
-        <v>96.8</v>
-      </c>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n"/>
       <c r="P15" s="3" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>19.8</v>
@@ -1690,11 +1704,11 @@
       <c r="R15" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="S15" s="8" t="n">
+      <c r="S15" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>73</v>
+        <v>373</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>6.2</v>
@@ -1706,13 +1720,13 @@
         <v>15.7</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>18</v>
+        <v>1.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>885.5</v>
+        <v>341</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1728,72 +1742,78 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1425.9</v>
+        <v>141.6</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>114.8</v>
+        <v>14.8</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>8.4</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>91.09999999999999</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1107.4</v>
+        <v>47.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>644.1</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>5.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>4.1</v>
-      </c>
+        <v>6.9</v>
+      </c>
+      <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="n">
         <v>73.2</v>
       </c>
-      <c r="M16" s="3" t="n"/>
-      <c r="N16" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O16" s="3" t="n"/>
+      <c r="M16" s="3" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5117
+18
+</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>2.9</v>
+      </c>
       <c r="P16" s="3" t="n">
-        <v>0.1</v>
+        <v>6</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>6.3</v>
+        <v>23.4</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>32.4</v>
+        <v>3994.5</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>14.8</v>
+        <v>44.8</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>184.5</v>
+        <v>84.3</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>28.6</v>
+        <v>25.6</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>17.5</v>
+        <v>56.1</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>92</v>
+        <v>48.2</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>11.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1809,47 +1829,47 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1.1</v>
+        <v>25</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>13.8</v>
+        <v>34.3</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>18.8</v>
+        <v>48.1</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>29.5</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>12.9</v>
+        <v>1.9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1.2</v>
+        <v>7.9</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="K17" s="3" t="n"/>
+      <c r="K17" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="L17" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="N17" s="3" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="N17" s="3" t="n"/>
       <c r="O17" s="3" t="n">
-        <v>2.1</v>
+        <v>9.1</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>16.7</v>
@@ -1858,25 +1878,25 @@
         <v>17.6</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v>16.9</v>
+        <v>0.5</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>15.7</v>
+        <v>1.8</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>86.7</v>
+        <v>17.2</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>50.2</v>
+        <v>9.1</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1892,49 +1912,53 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>225</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>24.9</v>
+        <v>428.5</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>9.1</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>12.3</v>
+        <v>13.5</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>18.4</v>
+        <v>1.4</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
+        <v>10.9</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>3.6</v>
+      </c>
       <c r="K18" s="3" t="n">
-        <v>0</v>
+        <v>18.7</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="M18" s="8" t="n">
+      <c r="M18" s="3" t="n">
         <v>13</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>14.8</v>
+        <v>18.1</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>92</v>
       </c>
       <c r="P18" s="3" t="n"/>
       <c r="Q18" s="3" t="n">
-        <v>3.5</v>
+        <v>21.8</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>1</v>
+        <v>17.8</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>6.1</v>
@@ -1945,17 +1969,17 @@
       <c r="V18" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="W18" s="8" t="n">
-        <v>16</v>
+      <c r="W18" s="3" t="n">
+        <v>26</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>17.2</v>
+        <v>1</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>2</v>
+        <v>410.4</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1971,7 +1995,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>428.5</v>
+        <v>440.6</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>25</v>
@@ -1979,38 +2003,40 @@
       <c r="E19" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>19.5</v>
+      <c r="F19" s="8" t="n">
+        <v>95.2</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="H19" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K19" s="8" t="n">
-        <v>18.7</v>
+        <v>5.4</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>5.6</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="M19" s="8" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>92</v>
-      </c>
+      <c r="M19" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+7
+</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="n"/>
       <c r="P19" s="3" t="n">
-        <v>51.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>24.9</v>
@@ -2019,28 +2045,28 @@
         <v>18.1</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v>14.4</v>
+        <v>8</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="W19" s="8" t="n">
-        <v>67.2</v>
+        <v>1.8</v>
+      </c>
+      <c r="W19" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>17</v>
+        <v>18.3</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>8.1</v>
+        <v>810.5</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>40.1</v>
+        <v>4.4</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2056,72 +2082,74 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>440.6</v>
+        <v>15.1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="E20" s="8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E20" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>17.5</v>
+        <v>1.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>16.9</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="n">
-        <v>18.8</v>
-      </c>
+      <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="n">
-        <v>5.6</v>
+        <v>10.9</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="M20" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="N20" s="3" t="n">
-        <v>1.1</v>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+7
+</t>
+        </is>
       </c>
       <c r="O20" s="3" t="n"/>
       <c r="P20" s="3" t="n">
-        <v>10.8</v>
+        <v>1.5</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="R20" s="8" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R20" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>76.8</v>
+        <v>46.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v>17.8</v>
+        <v>18.5</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>11.6</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2137,29 +2165,31 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>153.1</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>21.9</v>
+        <v>2461.7</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>41.9</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>12.7</v>
+        <v>14.7</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>7.2</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="I21" s="3" t="n"/>
+        <v>14.1</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="J21" s="3" t="n">
         <v>11.5</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>10.9</v>
+        <v>3</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>16.2</v>
@@ -2167,15 +2197,17 @@
       <c r="M21" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="N21" s="8" t="n">
-        <v>97</v>
-      </c>
-      <c r="O21" s="3" t="n"/>
+      <c r="N21" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="P21" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>21.5</v>
+        <v>7.8</v>
+      </c>
+      <c r="Q21" s="8" t="n">
+        <v>41.4</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>18.1</v>
@@ -2184,25 +2216,25 @@
         <v>18.9</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>74.8</v>
+        <v>4</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>1.8</v>
+        <v>17</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>18.6</v>
+        <v>1.2</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>92</v>
+        <v>4.8</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>11.6</v>
+        <v>2.8</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2218,74 +2250,70 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>261.7</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>14.9</v>
+        <v>13.3</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>14.4</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="H22" s="8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H22" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1.8</v>
+        <v>10.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L22" s="8" t="n">
-        <v>12.5</v>
+        <v>33.2</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="N22" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="P22" s="3" t="n"/>
+      <c r="N22" s="3" t="n"/>
+      <c r="O22" s="3" t="n"/>
+      <c r="P22" s="3" t="n">
+        <v>7</v>
+      </c>
       <c r="Q22" s="3" t="n">
-        <v>20.4</v>
+        <v>26.4</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="S22" s="8" t="n">
-        <v>17.8</v>
+      <c r="S22" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>16.2</v>
+        <v>56.2</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>17.5</v>
+        <v>1.5</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="X22" s="3" t="n">
-        <v>18.9</v>
-      </c>
+      <c r="X22" s="3" t="n"/>
       <c r="Y22" s="3" t="n">
-        <v>94.5</v>
+        <v>45.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2301,43 +2329,41 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>123.3</v>
+        <v>147.7</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>113.1</v>
       </c>
-      <c r="E23" s="3" t="n"/>
+      <c r="E23" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="F23" s="3" t="n">
-        <v>91.8</v>
+        <v>9.4</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>43.7</v>
       </c>
-      <c r="H23" s="3" t="n">
-        <v>617</v>
-      </c>
+      <c r="H23" s="3" t="n"/>
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>3321.1</v>
-      </c>
+        <v>7.3</v>
+      </c>
+      <c r="K23" s="3" t="n"/>
       <c r="L23" s="3" t="n">
         <v>76.2</v>
       </c>
       <c r="M23" s="3" t="n"/>
       <c r="N23" s="3" t="n">
-        <v>1.6</v>
+        <v>7.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>17</v>
+        <v>1.4</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>109</v>
+        <v>179.8</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>88.8</v>
@@ -2346,25 +2372,25 @@
         <v>90.2</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>414.1</v>
+        <v>41.9</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>40.6</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>94.2</v>
+        <v>44.2</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>16.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>7.2</v>
+        <v>2.3</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>499.5</v>
+        <v>0.1</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>10.9</v>
+        <v>158.1</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2380,58 +2406,54 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1477.9</v>
+        <v>1.4</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>13.9</v>
+        <v>1.9</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>1.4</v>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="H24" s="3" t="n"/>
       <c r="I24" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="n">
-        <v>15.2</v>
+        <v>1.2</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="N24" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="N24" s="3" t="n"/>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+111
+</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="n"/>
       <c r="Q24" s="3" t="n">
-        <v>21.8</v>
+        <v>1.8</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="S24" s="3" t="n">
-        <v>18.1</v>
+      <c r="S24" s="8" t="n">
+        <v>28.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>8.1</v>
@@ -2440,16 +2462,16 @@
         <v>18.3</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>18.3</v>
+        <v>1.8</v>
+      </c>
+      <c r="X24" s="8" t="n">
+        <v>11.1</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>94</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>158.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2465,51 +2487,49 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>95.40000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>22.6</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>13.8</v>
+        <v>1.6</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>18.1</v>
+        <v>1.8</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>46.1</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.1</v>
+        <v>14.6</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>90.09999999999999</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>5.1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="M25" s="8" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="M25" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="P25" s="3" t="n"/>
-      <c r="Q25" s="3" t="n">
-        <v>64.59999999999999</v>
+        <v>1.8</v>
+      </c>
+      <c r="O25" s="3" t="n"/>
+      <c r="P25" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>145.4</v>
       </c>
       <c r="R25" s="3" t="n"/>
       <c r="S25" s="3" t="n">
-        <v>11.6</v>
+        <v>17.6</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>6.6</v>
@@ -2521,16 +2541,16 @@
         <v>16.6</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>19.1</v>
+        <v>18</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>94</v>
+        <v>88.5</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2546,22 +2566,22 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>890.4</v>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>22.5</v>
+        <v>28.8</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>2.5</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>18.9</v>
+      <c r="F26" s="8" t="n">
+        <v>89.09999999999999</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>1.3</v>
+        <v>13.8</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.4</v>
@@ -2569,53 +2589,57 @@
       <c r="J26" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="K26" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L26" s="8" t="n">
-        <v>84.59999999999999</v>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+1198
+</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>14.1</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>1.4</v>
+        <v>40.6</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="R26" s="8" t="n">
+      <c r="R26" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>1713</v>
+        <v>3</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>17.9</v>
+        <v>12.5</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>46.5</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>88.5</v>
+        <v>91.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2631,10 +2655,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>326</v>
+        <v>53.5</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>23.5</v>
+        <v>13.5</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>14.4</v>
@@ -2643,7 +2667,7 @@
         <v>18.9</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>14.9</v>
@@ -2653,35 +2677,37 @@
         <v>2.1</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="L27" s="3" t="n"/>
-      <c r="M27" s="8" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="M27" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.1</v>
+        <v>15.1</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>195</v>
+        <v>95</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q27" s="8" t="n">
-        <v>10.8</v>
+        <v>16.8</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>17.9</v>
+        <v>1.9</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="V27" s="3" t="n">
         <v>17.8</v>
@@ -2690,13 +2716,13 @@
         <v>16.8</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>18.5</v>
+        <v>15.8</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>91</v>
+        <v>83.8</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2712,58 +2738,62 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>281.8</v>
+        <v>289.8</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>53.8</v>
+        <v>41.8</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>17.9</v>
+        <v>1.9</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.9</v>
+        <v>8.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>15.4</v>
+        <v>7.1</v>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9799791979277
+2 8
+</t>
+        </is>
       </c>
       <c r="L28" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="M28" s="8" t="n">
+      <c r="M28" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="P28" s="3" t="n">
-        <v>0.8</v>
+      <c r="P28" s="8" t="n">
+        <v>10.8</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="S28" s="8" t="n">
-        <v>76.8</v>
+      <c r="S28" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>72.8</v>
+        <v>2.8</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>6.6</v>
@@ -2774,14 +2804,14 @@
       <c r="W28" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="X28" s="3" t="n">
-        <v>15.8</v>
+      <c r="X28" s="8" t="n">
+        <v>85.09999999999999</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>830.8</v>
+        <v>85</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2797,16 +2827,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2305.9</v>
-      </c>
-      <c r="D29" s="8" t="n">
-        <v>121.9</v>
+        <v>199.9</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>17.9</v>
+        <v>1.9</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>8.1</v>
@@ -2815,41 +2845,41 @@
         <v>13.8</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>12</v>
+        <v>2.6</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L29" s="8" t="n">
-        <v>84.90000000000001</v>
+        <v>25</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>14.9</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O29" s="3" t="n"/>
-      <c r="P29" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>714.4</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P29" s="3" t="n"/>
       <c r="Q29" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>19.8</v>
+        <v>17.8</v>
       </c>
       <c r="S29" s="8" t="n">
-        <v>82.09999999999999</v>
+        <v>12.1</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>18</v>
+        <v>1.8</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>7.8</v>
+        <v>0.8</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>18.8</v>
@@ -2857,11 +2887,9 @@
       <c r="W29" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="X29" s="3" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="X29" s="3" t="n"/>
       <c r="Y29" s="3" t="n">
-        <v>85</v>
+        <v>147.4</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>3.2</v>
@@ -2879,63 +2907,90 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>289.8</v>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1921
+188181
+</t>
+        </is>
       </c>
       <c r="D30" s="3" t="n">
         <v>716.2</v>
       </c>
-      <c r="E30" s="3" t="n"/>
+      <c r="E30" s="3" t="n">
+        <v>68.59999999999999</v>
+      </c>
       <c r="F30" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>966.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>43</v>
+        <v>4570</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>6661.1</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>11565.6</v>
+        <v>26.6</v>
       </c>
       <c r="J30" s="3" t="n"/>
-      <c r="K30" s="3" t="n">
-        <v>350.1</v>
-      </c>
-      <c r="L30" s="3" t="n"/>
+      <c r="K30" s="3" t="n"/>
+      <c r="L30" s="3" t="n">
+        <v>719.7</v>
+      </c>
       <c r="M30" s="3" t="n">
-        <v>77.3</v>
+        <v>0.1</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>71.7</v>
+        <v>4.1</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>20.1</v>
+        <v>1</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>1056.2</v>
+        <v>15.2</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>824.4</v>
       </c>
-      <c r="S30" s="3" t="n"/>
-      <c r="T30" s="3" t="n"/>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">368883
+101
+</t>
+        </is>
+      </c>
+      <c r="T30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9242175
+993 6
+</t>
+        </is>
+      </c>
       <c r="U30" s="3" t="n">
-        <v>248.1</v>
+        <v>246.1</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="W30" s="3" t="n"/>
-      <c r="X30" s="3" t="n"/>
+        <v>1.8</v>
+      </c>
+      <c r="W30" s="3" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">777
+1
+17
+</t>
+        </is>
+      </c>
       <c r="Y30" s="3" t="n">
-        <v>14.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>3.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2951,10 +3006,10 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.1</v>
+        <v>22</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>22.8</v>
+        <v>2.5</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>13.7</v>
@@ -2974,51 +3029,49 @@
       <c r="J31" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="K31" s="3" t="n"/>
+      <c r="K31" s="3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="L31" s="3" t="n">
-        <v>14.9</v>
+        <v>14.2</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="N31" s="8" t="n">
-        <v>170.5</v>
+      <c r="N31" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>21</v>
+        <v>2.1</v>
       </c>
       <c r="R31" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="S31" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>72.3</v>
-      </c>
+      <c r="S31" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="T31" s="3" t="n"/>
       <c r="U31" s="3" t="n">
         <v>6.9</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>12.6</v>
+        <v>1.6</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>17.7</v>
-      </c>
+        <v>6.2</v>
+      </c>
+      <c r="X31" s="3" t="n"/>
       <c r="Y31" s="3" t="n">
-        <v>88.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>7.5</v>
+        <v>2.4</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3034,59 +3087,61 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>322</v>
-      </c>
-      <c r="D32" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D32" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>13.1</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>8.9</v>
+        <v>1.3</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>13.4</v>
+        <v>15.4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>12.7</v>
+        <v>0.7</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>16.3</v>
+        <v>1.3</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="N32" s="3" t="n"/>
+        <v>445.1</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>7.8</v>
+      </c>
       <c r="O32" s="3" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="3" t="n">
         <v>17</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="S32" s="3" t="n">
-        <v>17</v>
+      <c r="S32" s="8" t="n">
+        <v>90</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>90</v>
+        <v>51.5</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="V32" s="3" t="n">
         <v>15.9</v>
@@ -3095,11 +3150,17 @@
         <v>15.6</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y32" s="3" t="n"/>
+        <v>16.8</v>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+710
+</t>
+        </is>
+      </c>
       <c r="Z32" s="3" t="n">
-        <v>2.4</v>
+        <v>8.5</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3115,76 +3176,76 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>235.5</v>
+        <v>482.8</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>24.9</v>
+        <v>2.8</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="F33" s="8" t="n">
-        <v>88.2</v>
+      <c r="F33" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H33" s="8" t="n">
-        <v>78.59999999999999</v>
+        <v>1.7</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2.6</v>
+        <v>22.6</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="K33" s="8" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="L33" s="8" t="n">
+      <c r="K33" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="L33" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>13</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>1.8</v>
+        <v>7.8</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>93</v>
+        <v>3</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q33" s="8" t="n">
-        <v>24.8</v>
+        <v>1</v>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <v>13.8</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>15.2</v>
+        <v>1.2</v>
       </c>
       <c r="T33" s="3" t="n">
         <v>51.5</v>
       </c>
-      <c r="U33" s="8" t="n">
-        <v>114.4</v>
+      <c r="U33" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>18</v>
+        <v>11.6</v>
       </c>
       <c r="W33" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>16</v>
+        <v>16.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>71.8</v>
+        <v>80.8</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3202,20 +3263,23 @@
       <c r="C34" s="3" t="n">
         <v>482.8</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.6</v>
+        <v>11.5</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112179 1
+</t>
+        </is>
       </c>
       <c r="I34" s="3" t="n">
         <v>2.5</v>
@@ -3224,49 +3288,57 @@
         <v>3.9</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="N34" s="3" t="n">
-        <v>1.8</v>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+1
+</t>
+        </is>
       </c>
       <c r="O34" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>23.9</v>
+        <v>15.9</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="S34" s="8" t="n">
-        <v>16.8</v>
+        <v>17.2</v>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v>15.2</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>56.8</v>
+        <v>714.4</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="V34" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V34" s="3" t="n">
         <v>18</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="X34" s="8" t="n">
+      <c r="X34" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="Y34" s="3" t="n">
-        <v>21</v>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+247
+</t>
+        </is>
       </c>
       <c r="Z34" s="3" t="n">
         <v>4.2</v>
@@ -3285,22 +3357,22 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>482.8</v>
+        <v>492.8</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>1215</v>
+        <v>50.1</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="G35" s="8" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="H35" s="8" t="n">
-        <v>12.9</v>
+        <v>43.6</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>2.4</v>
@@ -3309,49 +3381,53 @@
         <v>4</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="M35" s="8" t="n">
+      <c r="M35" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O35" s="3" t="n">
-        <v>98</v>
+        <v>91</v>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14181
+60
+</t>
+        </is>
       </c>
       <c r="P35" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q35" s="3" t="n">
-        <v>84.5</v>
+      <c r="Q35" s="8" t="n">
+        <v>45.7</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>18.5</v>
+        <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>600.9</v>
+        <v>56.8</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="V35" s="8" t="n">
-        <v>20.7</v>
+        <v>206.7</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="X35" s="3" t="n">
-        <v>18.5</v>
+        <v>11.1</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>85.09999999999999</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>75.8</v>
+        <v>79.8</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>6</v>
@@ -3372,26 +3448,26 @@
       <c r="C36" s="3" t="n">
         <v>498.9</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="E36" s="8" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="F36" s="8" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="G36" s="8" t="n">
+      <c r="E36" s="3" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G36" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="I36" s="3" t="n">
-        <v>2.2</v>
+      <c r="I36" s="8" t="n">
+        <v>23.5</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0</v>
@@ -3400,31 +3476,29 @@
         <v>16.6</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>11.5</v>
-      </c>
+        <v>15.6</v>
+      </c>
+      <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="n">
-        <v>91</v>
+        <v>918</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="Q36" s="8" t="n">
-        <v>14.1</v>
+        <v>44.1</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="S36" s="3" t="n">
-        <v>11</v>
+      <c r="S36" s="8" t="n">
+        <v>82.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>55.1</v>
+        <v>60.8</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>13.2</v>
+        <v>1.2</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>18.4</v>
@@ -3432,14 +3506,14 @@
       <c r="W36" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="X36" s="3" t="n">
-        <v>16.6</v>
+      <c r="X36" s="8" t="n">
+        <v>66.09999999999999</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>14.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3455,74 +3529,72 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2492.3</v>
+        <v>928</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>7.9</v>
+        <v>119.4</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>65.8</v>
+        <v>76.8</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>53.3</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>61.9</v>
+        <v>613.9</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1110.6</v>
+        <v>1.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>48.5</v>
+        <v>0.6</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>121.8</v>
+        <v>12.1</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>175.7</v>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>7.2</v>
-      </c>
+        <v>75.7</v>
+      </c>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="n">
-        <v>149</v>
+        <v>4498</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>113.4</v>
+        <v>11.3</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>81.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>24.8</v>
+        <v>1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>434.4</v>
+        <v>58.1</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>234.8</v>
+        <v>4.8</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>7.1</v>
+        <v>377.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>809.8</v>
+        <v>804.8</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="Y37" s="3" t="n"/>
+        <v>85.2</v>
+      </c>
+      <c r="Y37" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Z37" s="3" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3538,7 +3610,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>438.6</v>
+        <v>0.4</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>23.8</v>
@@ -3547,53 +3619,62 @@
         <v>13.2</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>18.5</v>
+        <v>1.5</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>12.3</v>
+        <v>2.8</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>12.1</v>
+        <v>2.1</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K38" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="n">
-        <v>15.1</v>
+        <v>1.5</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O38" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P38" s="3" t="n">
-        <v>11.8</v>
+        <v>89.90000000000001</v>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61718682
+68
+8987
+</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 8
+21 0
+</t>
+        </is>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="R38" s="3" t="n">
-        <v>17.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+14
+</t>
+        </is>
       </c>
       <c r="S38" s="3" t="n">
-        <v>17</v>
+        <v>84.8</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>11</v>
-      </c>
+        <v>31.4</v>
+      </c>
+      <c r="U38" s="3" t="n"/>
       <c r="V38" s="3" t="n">
         <v>18.2</v>
       </c>
@@ -3601,7 +3682,7 @@
         <v>16.1</v>
       </c>
       <c r="X38" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="Y38" s="3" t="n">
         <v>81.90000000000001</v>
@@ -3623,74 +3704,78 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>395.5</v>
+        <v>58.3</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>24.5</v>
+        <v>14.5</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>13.6</v>
+        <v>1</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>23.5</v>
+        <v>7.1</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>3.2</v>
+        <v>71.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>9.9</v>
+        <v>5.7</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>46.1</v>
+        <v>46.6</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>50.1</v>
+        <v>5</v>
       </c>
       <c r="N39" s="3" t="n"/>
-      <c r="O39" s="3" t="n">
-        <v>89.8</v>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+8917
+</t>
+        </is>
       </c>
       <c r="P39" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q39" s="3" t="n">
-        <v>25.8</v>
+      <c r="Q39" s="8" t="n">
+        <v>53.6</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>7.7</v>
+        <v>11.6</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>52</v>
+        <v>64.7</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v>191.1</v>
+        <v>1</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>15.7</v>
+        <v>16</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>11.4</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>6.4</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3706,10 +3791,10 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>5452.1</v>
+        <v>545.1</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>13.8</v>
@@ -3720,59 +3805,63 @@
       <c r="G40" s="3" t="n">
         <v>10.7</v>
       </c>
-      <c r="H40" s="8" t="n">
+      <c r="H40" s="3" t="n">
         <v>11.5</v>
       </c>
-      <c r="I40" s="3" t="n">
-        <v>3</v>
+      <c r="I40" s="8" t="n">
+        <v>353</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>14.7</v>
+        <v>4.7</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L40" s="8" t="n">
         <v>48.1</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>13.6</v>
+        <v>353.6</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O40" s="3" t="n">
-        <v>21</v>
+        <v>88.90000000000001</v>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+6
+</t>
+        </is>
       </c>
       <c r="P40" s="3" t="n">
         <v>2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>23.8</v>
+        <v>13.8</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>17.8</v>
+        <v>1.1</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>58.5</v>
       </c>
-      <c r="U40" s="8" t="n">
-        <v>12</v>
+      <c r="U40" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="W40" s="3" t="n">
-        <v>16</v>
+      <c r="W40" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>16.9</v>
+        <v>13.8</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>72</v>
+        <v>2.8</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>6.2</v>
@@ -3800,19 +3889,19 @@
         <v>12.5</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="G41" s="8" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H41" s="8" t="n">
-        <v>10.8</v>
+        <v>18.5</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="J41" s="8" t="n">
-        <v>14</v>
+        <v>24.1</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
@@ -3820,26 +3909,26 @@
       <c r="L41" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="M41" s="8" t="n">
-        <v>38.9</v>
+      <c r="M41" s="3" t="n">
+        <v>13.7</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>1.1</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>8770.1</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R41" s="8" t="n">
-        <v>80.8</v>
+      <c r="Q41" s="8" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>17.8</v>
+        <v>1.8</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>62.5</v>
@@ -3847,11 +3936,11 @@
       <c r="U41" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V41" s="3" t="n">
-        <v>19</v>
+      <c r="V41" s="8" t="n">
+        <v>96</v>
       </c>
       <c r="W41" s="8" t="n">
-        <v>17</v>
+        <v>658.5</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>18.2</v>
@@ -3878,75 +3967,82 @@
       <c r="C42" s="3" t="n">
         <v>340.1</v>
       </c>
-      <c r="D42" s="8" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>14.9</v>
+      <c r="D42" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+181
+</t>
+        </is>
       </c>
       <c r="F42" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="G42" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="H42" s="8" t="n">
+      <c r="G42" s="8" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="H42" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="J42" s="8" t="n">
-        <v>14.6</v>
+      <c r="J42" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L42" s="8" t="n">
-        <v>621.1</v>
-      </c>
-      <c r="M42" s="8" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N42" s="3" t="n"/>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 111
+        <v>0.1</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2924
+991
 </t>
         </is>
       </c>
+      <c r="O42" s="3" t="n">
+        <v>12</v>
+      </c>
       <c r="P42" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Q42" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="R42" s="8" t="n">
-        <v>67.09999999999999</v>
+      <c r="R42" s="3" t="n">
+        <v>16.1</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>16</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>60.5</v>
+        <v>6.5</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v>18.9</v>
+        <v>19.4</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X42" s="8" t="n">
-        <v>89.8</v>
+        <v>15.1</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>87</v>
+        <v>81.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>2.6</v>
+        <v>53.7</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3962,76 +4058,76 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>5310.9</v>
-      </c>
-      <c r="D43" s="8" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>18.1</v>
+        <v>57</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>807</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H43" s="8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H43" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="K43" s="3" t="n">
-        <v>10</v>
+      <c r="K43" s="8" t="n">
+        <v>0.8</v>
       </c>
       <c r="L43" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="N43" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>927.1</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q43" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="X43" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="M43" s="8" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="N43" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="O43" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Q43" s="8" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="R43" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="S43" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="T43" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="W43" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="X43" s="3" t="n">
-        <v>16.2</v>
-      </c>
       <c r="Y43" s="3" t="n">
-        <v>81.8</v>
+        <v>78</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4047,25 +4143,25 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>857.1</v>
+        <v>5.1</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>23.4</v>
+        <v>63.4</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>12.6</v>
+        <v>1.7</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>18</v>
+        <v>182.5</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H44" s="8" t="n">
+        <v>61</v>
+      </c>
+      <c r="H44" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>14.6</v>
+        <v>2.6</v>
       </c>
       <c r="J44" s="3" t="n">
         <v>5</v>
@@ -4073,20 +4169,24 @@
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="8" t="n">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="M44" s="8" t="n">
-        <v>89.59999999999999</v>
+      <c r="L44" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>15.6</v>
       </c>
       <c r="N44" s="8" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>91.8</v>
+        <v>40.9</v>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+1272971
+</t>
+        </is>
       </c>
       <c r="P44" s="3" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>22.2</v>
@@ -4095,28 +4195,28 @@
         <v>16.7</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>12.9</v>
+        <v>1.9</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>159.5</v>
-      </c>
-      <c r="U44" s="8" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="U44" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="V44" s="3" t="n">
-        <v>18.1</v>
+      <c r="V44" s="8" t="n">
+        <v>11.8</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>14.8</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="X44" s="8" t="n">
+        <v>66.8</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>724</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>28.7</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4132,75 +4232,75 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>228.3</v>
+        <v>283</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>1.1</v>
+        <v>7.7</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>2.4</v>
+        <v>13.3</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>10.5</v>
+        <v>12.4</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>621</v>
+        <v>61</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>70.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>16.9</v>
+        <v>15.2</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>25.2</v>
+        <v>215.2</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>898.5</v>
+        <v>28.4</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>851.1</v>
+        <v>887.1</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="O45" s="3" t="n">
-        <v>540.9</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="O45" s="3" t="n"/>
       <c r="P45" s="3" t="n">
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>975.6</v>
+        <v>979.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>3561.1</v>
+        <v>351.1</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="V45" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>95.8</v>
+        <v>0.6</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>9292.6</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>166.8</v>
-      </c>
-      <c r="Z45" s="3" t="n"/>
+        <v>7.8</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>28.7</v>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4217,16 +4317,18 @@
       <c r="C46" s="3" t="n">
         <v>497</v>
       </c>
-      <c r="D46" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">818
+4236
+</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n"/>
       <c r="F46" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G46" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G46" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="H46" s="3" t="n">
@@ -4238,18 +4340,18 @@
       <c r="J46" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K46" s="3" t="n"/>
+      <c r="K46" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="L46" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
+        <v>14.1</v>
+      </c>
+      <c r="M46" s="3" t="n"/>
       <c r="N46" s="3" t="n">
-        <v>15.8</v>
+        <v>1.2</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>1.8</v>
@@ -4257,29 +4359,27 @@
       <c r="Q46" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="R46" s="8" t="n">
-        <v>71.8</v>
+      <c r="R46" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>58.5</v>
+        <v>0.5</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v>18.6</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="V46" s="3" t="n"/>
       <c r="W46" s="3" t="n">
-        <v>15.9</v>
+        <v>0.1</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>27.8</v>
+        <v>7.8</v>
       </c>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_decimal_place_correction.xlsx
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>582.3</v>
+        <v>582.9</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>25.1</v>
@@ -744,24 +744,38 @@
       <c r="E4" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="n">
+        <v>19.3</v>
+      </c>
       <c r="G4" s="3" t="n">
         <v>11.5</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
+        <v>13.1</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>14.2</v>
+      </c>
       <c r="L4" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr"/>
-      <c r="O4" s="3" t="inlineStr"/>
+        <v>11.7</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>87</v>
+      </c>
       <c r="P4" s="3" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>25</v>
@@ -772,11 +786,17 @@
       <c r="S4" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="n">
+        <v>152</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v>120.7</v>
+      </c>
       <c r="W4" s="3" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
@@ -795,37 +815,55 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>388.8</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr"/>
+        <v>288.9</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>10.8</v>
+      </c>
       <c r="E5" s="3" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="F5" s="3" t="inlineStr"/>
+        <v>14.2</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>19.1</v>
+      </c>
       <c r="G5" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>12.8</v>
+        <v>12.3</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K5" s="3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>12.7</v>
+      </c>
       <c r="L5" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="S5" s="8" t="n">
+        <v>16.7</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>52</v>
@@ -836,13 +874,15 @@
       <c r="V5" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="W5" s="8" t="n">
+      <c r="W5" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Y5" s="3" t="n">
+        <v>75.5</v>
+      </c>
       <c r="Z5" s="3" t="n">
         <v>6</v>
       </c>
@@ -860,32 +900,56 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2508.9</v>
-      </c>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="n">
-        <v>13.6</v>
+        <v>508.9</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+        <v>11.2</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="J6" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr"/>
+        <v>4.8</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>13.8</v>
+      </c>
       <c r="M6" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="N6" s="3" t="inlineStr"/>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="T6" s="3" t="n">
         <v>61.9</v>
       </c>
@@ -893,16 +957,20 @@
         <v>10.4</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="W6" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="W6" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X6" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="Y6" s="3" t="inlineStr"/>
-      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="X6" s="8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>12.8</v>
+      </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -919,51 +987,73 @@
       <c r="C7" s="3" t="n">
         <v>512.9</v>
       </c>
-      <c r="D7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="n">
+        <v>23.9</v>
+      </c>
       <c r="E7" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>18.8</v>
+      <c r="F7" s="8" t="n">
+        <v>189.8</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>10.7</v>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="J7" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N7" s="3" t="inlineStr"/>
+        <v>3.4</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>18.8</v>
+      </c>
       <c r="O7" s="3" t="n">
-        <v>41</v>
+        <v>593</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>11.8</v>
+        <v>1.6</v>
       </c>
       <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="n">
+        <v>17.6</v>
+      </c>
       <c r="S7" s="3" t="n">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>59.1</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>191.8</v>
-      </c>
-      <c r="V7" s="3" t="inlineStr"/>
-      <c r="W7" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="W7" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="X7" s="3" t="inlineStr"/>
-      <c r="Y7" s="3" t="inlineStr"/>
-      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -980,9 +1070,11 @@
       <c r="C8" s="3" t="n">
         <v>229.8</v>
       </c>
-      <c r="D8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="n">
+        <v>41.9</v>
+      </c>
       <c r="E8" s="3" t="n">
-        <v>12.8</v>
+        <v>13.8</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>17.7</v>
@@ -990,7 +1082,9 @@
       <c r="G8" s="3" t="n">
         <v>7.7</v>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="n">
+        <v>12.9</v>
+      </c>
       <c r="I8" s="3" t="n">
         <v>1.8</v>
       </c>
@@ -998,7 +1092,7 @@
         <v>1.8</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>7.7</v>
+        <v>27.2</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>15.1</v>
@@ -1006,24 +1100,36 @@
       <c r="M8" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>98</v>
+      </c>
       <c r="P8" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="T8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="S8" s="8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>76</v>
+      </c>
       <c r="U8" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="W8" s="3" t="inlineStr"/>
+      <c r="W8" s="3" t="n">
+        <v>16</v>
+      </c>
       <c r="X8" s="3" t="inlineStr"/>
       <c r="Y8" s="3" t="inlineStr"/>
       <c r="Z8" s="3" t="inlineStr"/>
@@ -1047,55 +1153,71 @@
         <v>118.5</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>93.09999999999999</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>269.4</v>
+        <v>881.5</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+        <v>65.09999999999999</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>10.5</v>
+      </c>
       <c r="J9" s="3" t="n">
-        <v>116.4</v>
+        <v>16.9</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr"/>
+        <v>31.1</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>60.7</v>
+      </c>
       <c r="N9" s="3" t="n">
-        <v>14.6</v>
+        <v>86</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>459</v>
+        <v>959</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1114</v>
+        <v>1194</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr"/>
-      <c r="U9" s="3" t="inlineStr"/>
+        <v>88.09999999999999</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>2162.6</v>
+      </c>
+      <c r="U9" s="3" t="n">
+        <v>22</v>
+      </c>
       <c r="V9" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="W9" s="3" t="inlineStr"/>
+        <v>959</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="X9" s="3" t="n">
-        <v>17.9</v>
+        <v>89.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z9" s="3" t="inlineStr"/>
+        <v>419.8</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1109,45 +1231,75 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="3" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="n">
+        <v>449</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>3.3</v>
+      </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr"/>
-      <c r="N10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>15.8</v>
+      </c>
       <c r="O10" s="3" t="n">
-        <v>459</v>
-      </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
+        <v>91.8</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>85.8</v>
+      </c>
       <c r="R10" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr"/>
+        <v>17.6</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>62.9</v>
+      </c>
       <c r="U10" s="3" t="n">
-        <v>530.1</v>
+        <v>10.6</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="W10" s="8" t="n">
-        <v>90.8</v>
+        <v>18.8</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>89.7</v>
+        <v>17.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>415</v>
+        <v>83</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>19.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1163,53 +1315,63 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>9445</v>
+        <v>221.8</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>23.7</v>
+        <v>22.5</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>13.5</v>
+        <v>19.7</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>18.6</v>
+        <v>18.1</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>10.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr"/>
+        <v>12.8</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="J11" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
+        <v>0.7</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>10.8</v>
+      </c>
       <c r="L11" s="3" t="n">
-        <v>14.7</v>
+        <v>1.2</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q11" s="3" t="inlineStr"/>
+        <v>11.8</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="P11" s="8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="R11" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="T11" s="3" t="inlineStr"/>
+        <v>15.9</v>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>28.4</v>
+      </c>
       <c r="U11" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V11" s="8" t="n">
+      <c r="V11" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="W11" s="3" t="n">
@@ -1236,57 +1398,77 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>291.8</v>
-      </c>
-      <c r="D12" s="3" t="inlineStr"/>
+        <v>229</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>22.4</v>
+      </c>
       <c r="E12" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="F12" s="3" t="inlineStr"/>
+        <v>13.3</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>17.9</v>
+      </c>
       <c r="G12" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr"/>
+        <v>9.1</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J12" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="8" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="N12" s="3" t="inlineStr"/>
-      <c r="O12" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>92.8</v>
+      </c>
       <c r="P12" s="3" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>19.8</v>
+        <v>20.5</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>22</v>
+        <v>17.1</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>19</v>
+        <v>17.7</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>188.4</v>
+        <v>74.5</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>9.9</v>
+        <v>6.2</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="W12" s="3" t="inlineStr"/>
-      <c r="X12" s="3" t="inlineStr"/>
-      <c r="Y12" s="3" t="inlineStr"/>
-      <c r="Z12" s="3" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="W12" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y12" s="3" t="n">
+        <v>240.8</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>3.8</v>
+      </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -1300,56 +1482,78 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="n">
+        <v>322</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>18.8</v>
+      </c>
       <c r="G13" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>13</v>
+        <v>28.1</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>15.1</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" s="3" t="inlineStr"/>
+        <v>1.7</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>15.7</v>
+      </c>
       <c r="L13" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q13" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="R13" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="M13" s="3" t="inlineStr"/>
-      <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="3" t="inlineStr"/>
-      <c r="P13" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q13" s="3" t="inlineStr"/>
-      <c r="R13" s="3" t="inlineStr"/>
       <c r="S13" s="3" t="n">
-        <v>17.7</v>
+        <v>1.6</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>14.9</v>
+        <v>90.5</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>6.2</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X13" s="8" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
+      </c>
+      <c r="X13" s="3" t="n">
+        <v>15.1</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z13" s="3" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1363,45 +1567,77 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="n">
-        <v>11.4</v>
+      <c r="C14" s="3" t="n">
+        <v>324</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>21.4</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="K14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="n">
+        <v>26.8</v>
+      </c>
       <c r="L14" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="M14" s="3" t="inlineStr"/>
+        <v>14.4</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>13.7</v>
+      </c>
       <c r="N14" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="O14" s="3" t="inlineStr"/>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
+        <v>15.4</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="T14" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="U14" s="3" t="inlineStr"/>
-      <c r="V14" s="3" t="inlineStr"/>
-      <c r="W14" s="8" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X14" s="3" t="inlineStr"/>
+        <v>71.90000000000001</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y14" s="3" t="n">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1416,45 +1652,75 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="n">
+        <v>307.9</v>
+      </c>
       <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>78.3</v>
+      </c>
       <c r="G15" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr"/>
+        <v>11.2</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="J15" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="3" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>14.2</v>
+      </c>
       <c r="M15" s="3" t="n">
-        <v>13.7</v>
+        <v>148.1</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="O15" s="3" t="inlineStr"/>
+        <v>15.5</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>96.8</v>
+      </c>
       <c r="P15" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
+        <v>1.6</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>16.9</v>
+      </c>
       <c r="T15" s="3" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="U15" s="3" t="inlineStr"/>
-      <c r="V15" s="3" t="inlineStr"/>
+        <v>73</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>16.6</v>
+      </c>
       <c r="W15" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="X15" s="3" t="inlineStr"/>
-      <c r="Y15" s="3" t="inlineStr"/>
+        <v>15.7</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y15" s="3" t="n">
+        <v>92</v>
+      </c>
       <c r="Z15" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1469,48 +1735,78 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="n">
+        <v>1972.2</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>91.09999999999999</v>
+      </c>
       <c r="G16" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="3" t="inlineStr"/>
+        <v>47.4</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>649.4</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>6.9</v>
+      </c>
       <c r="K16" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr"/>
+        <v>46.8</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>191.2</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>69.40000000000001</v>
+      </c>
       <c r="N16" s="3" t="n">
-        <v>18.5</v>
+        <v>1164.2</v>
       </c>
       <c r="O16" s="3" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q16" s="3" t="n">
         <v>96.90000000000001</v>
       </c>
-      <c r="P16" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>88.40000000000001</v>
+      </c>
       <c r="T16" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="U16" s="3" t="inlineStr"/>
+        <v>164.8</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>24.8</v>
+      </c>
       <c r="V16" s="3" t="n">
-        <v>16.6</v>
+        <v>84.5</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X16" s="3" t="inlineStr"/>
+        <v>180.6</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>85.09999999999999</v>
+      </c>
       <c r="Y16" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="Z16" s="3" t="inlineStr"/>
+        <v>488.8</v>
+      </c>
+      <c r="Z16" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1525,74 +1821,76 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1972.2</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>114.8</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>47.4</v>
+        <v>225</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>9.5</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>4.4</v>
+        <v>12.9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>1.2</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>21.4</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>46.8</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="M17" s="8" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="N17" s="8" t="n">
-        <v>16464.6</v>
-      </c>
-      <c r="O17" s="3" t="inlineStr"/>
+        <v>14.6</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>92.90000000000001</v>
+      </c>
       <c r="P17" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q17" s="8" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="R17" s="8" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="S17" s="8" t="n">
-        <v>88</v>
+        <v>1.2</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>324.5</v>
+        <v>18.9</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>24.2</v>
+        <v>9</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W17" s="8" t="n">
-        <v>718.6</v>
+        <v>16.9</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>15.7</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>86.09999999999999</v>
+        <v>17.2</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>2420.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1608,54 +1906,74 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>225</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="8" t="n">
-        <v>12.9</v>
+        <v>428.8</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>10.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>1.2</v>
+        <v>10.1</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="K18" s="3" t="inlineStr"/>
+        <v>3.6</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="L18" s="3" t="n">
-        <v>34.6</v>
+        <v>14</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="N18" s="3" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>14.4</v>
+      </c>
       <c r="O18" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>21.8</v>
+      </c>
       <c r="R18" s="3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>416.1</v>
+        <v>18.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="U18" s="3" t="inlineStr"/>
+        <v>69.09999999999999</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="V18" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X18" s="3" t="inlineStr"/>
-      <c r="Y18" s="3" t="inlineStr"/>
+        <v>16.8</v>
+      </c>
+      <c r="X18" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y18" s="3" t="n">
+        <v>81.8</v>
+      </c>
       <c r="Z18" s="3" t="n">
         <v>2</v>
       </c>
@@ -1673,54 +1991,74 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>428.5</v>
+        <v>840.6</v>
       </c>
       <c r="D19" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Q19" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="E19" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
-      <c r="K19" s="3" t="inlineStr"/>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q19" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R19" s="3" t="inlineStr"/>
-      <c r="S19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>17</v>
+      </c>
       <c r="T19" s="3" t="n">
-        <v>169.1</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>8</v>
+        <v>54</v>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v>14.4</v>
       </c>
       <c r="V19" s="3" t="inlineStr"/>
-      <c r="W19" s="3" t="inlineStr"/>
-      <c r="X19" s="3" t="inlineStr"/>
+      <c r="W19" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X19" s="8" t="n">
+        <v>18.8</v>
+      </c>
       <c r="Y19" s="3" t="n">
         <v>81</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>4</v>
+        <v>27.4</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -1736,47 +2074,77 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2440.6</v>
+        <v>153.1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
+        <v>24.9</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>17.8</v>
+      </c>
       <c r="G20" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="3" t="inlineStr"/>
-      <c r="N20" s="3" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="O20" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="W20" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X20" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Y20" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="P20" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Q20" s="3" t="inlineStr"/>
-      <c r="R20" s="3" t="inlineStr"/>
-      <c r="S20" s="3" t="inlineStr"/>
-      <c r="T20" s="3" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V20" s="3" t="inlineStr"/>
-      <c r="W20" s="3" t="inlineStr"/>
-      <c r="X20" s="3" t="inlineStr"/>
-      <c r="Y20" s="3" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="Z20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -1791,45 +2159,77 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>153.1</v>
+        <v>261.7</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
+        <v>20.6</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>11.9</v>
+      </c>
       <c r="K21" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="3" t="inlineStr"/>
+        <v>10.9</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="O21" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="3" t="inlineStr"/>
-      <c r="R21" s="3" t="inlineStr"/>
-      <c r="S21" s="3" t="inlineStr"/>
+        <v>90.8</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q21" s="8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="T21" s="3" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="U21" s="3" t="inlineStr"/>
-      <c r="V21" s="8" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="W21" s="3" t="inlineStr"/>
-      <c r="X21" s="3" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="W21" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="X21" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y21" s="3" t="n">
-        <v>192</v>
-      </c>
-      <c r="Z21" s="3" t="inlineStr"/>
+        <v>880.9</v>
+      </c>
+      <c r="Z21" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -1844,52 +2244,76 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1261.7</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr"/>
+        <v>123.3</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="J22" s="3" t="n">
-        <v>9.9</v>
+        <v>0.5</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="3" t="inlineStr"/>
-      <c r="N22" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="O22" s="3" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="P22" s="3" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="Q22" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="R22" s="3" t="inlineStr"/>
-      <c r="S22" s="3" t="n">
-        <v>18.9</v>
+        <v>20.4</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="S22" s="8" t="n">
+        <v>17.8</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>74</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="V22" s="3" t="inlineStr"/>
-      <c r="W22" s="3" t="inlineStr"/>
-      <c r="X22" s="3" t="inlineStr"/>
+        <v>6.2</v>
+      </c>
+      <c r="V22" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="W22" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="X22" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y22" s="3" t="n">
-        <v>870.9</v>
+        <v>94.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -1905,58 +2329,76 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>123.3</v>
+        <v>1921.2</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>120.6</v>
-      </c>
-      <c r="E23" s="3" t="inlineStr"/>
+        <v>11153.1</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>49.4</v>
+      </c>
       <c r="F23" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
+        <v>940.8</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>43.1</v>
+      </c>
       <c r="H23" s="3" t="n">
-        <v>93.40000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr"/>
+        <v>80.8</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="K23" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr"/>
+        <v>38.2</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>122.1</v>
+      </c>
       <c r="N23" s="3" t="n">
-        <v>1.6</v>
+        <v>816.4</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>91.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>11.8</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>120.4</v>
-      </c>
-      <c r="R23" s="3" t="inlineStr"/>
+        <v>109</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>88.8</v>
+      </c>
       <c r="S23" s="3" t="n">
-        <v>117.8</v>
+        <v>90</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>74</v>
+        <v>347.9</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="V23" s="3" t="inlineStr"/>
-      <c r="W23" s="3" t="inlineStr"/>
-      <c r="X23" s="3" t="inlineStr"/>
+        <v>40.6</v>
+      </c>
+      <c r="V23" s="3" t="n">
+        <v>918.9</v>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v>911.8</v>
+      </c>
       <c r="Y23" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>48.4</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>1.8</v>
+        <v>113.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -1972,74 +2414,76 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1983.2</v>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>13.1</v>
+        <v>215.4</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="G24" s="8" t="n">
-        <v>43.7</v>
+        <v>13.9</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>644.4</v>
+        <v>69.8</v>
       </c>
       <c r="I24" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="W24" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="Y24" s="3" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="Z24" s="3" t="n">
         <v>2.8</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>332.1</v>
-      </c>
-      <c r="L24" s="8" t="n">
-        <v>7162.1</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="N24" s="8" t="n">
-        <v>461.8</v>
-      </c>
-      <c r="O24" s="3" t="inlineStr"/>
-      <c r="P24" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q24" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="R24" s="3" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="T24" s="3" t="n">
-        <v>347.9</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>406.4</v>
-      </c>
-      <c r="V24" s="3" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="Y24" s="3" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="Z24" s="3" t="n">
-        <v>198.4</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2055,54 +2499,74 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>235.4</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F25" s="3" t="inlineStr"/>
+        <v>490.4</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="G25" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="H25" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>849.2</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>910.8</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="W25" s="8" t="n">
         <v>12.9</v>
       </c>
-      <c r="I25" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K25" s="3" t="inlineStr"/>
-      <c r="L25" s="3" t="inlineStr"/>
-      <c r="M25" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr"/>
-      <c r="O25" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="P25" s="3" t="inlineStr"/>
-      <c r="Q25" s="8" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="S25" s="3" t="n">
+      <c r="X25" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="T25" s="3" t="inlineStr"/>
-      <c r="U25" s="3" t="inlineStr"/>
-      <c r="V25" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="W25" s="3" t="inlineStr"/>
-      <c r="X25" s="3" t="inlineStr"/>
-      <c r="Y25" s="3" t="inlineStr"/>
+      <c r="Y25" s="3" t="n">
+        <v>94</v>
+      </c>
       <c r="Z25" s="3" t="n">
         <v>2.8</v>
       </c>
@@ -2120,53 +2584,77 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>490.4</v>
+        <v>287.8</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E26" s="3" t="inlineStr"/>
+        <v>23.5</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>14.4</v>
+      </c>
       <c r="F26" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="G26" s="3" t="inlineStr"/>
+        <v>18.9</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>8.9</v>
+      </c>
       <c r="H26" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="V26" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="I26" s="3" t="inlineStr"/>
-      <c r="J26" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
-      <c r="L26" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="M26" s="3" t="inlineStr"/>
-      <c r="N26" s="3" t="inlineStr"/>
-      <c r="O26" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="R26" s="3" t="inlineStr"/>
-      <c r="S26" s="8" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="T26" s="3" t="inlineStr"/>
-      <c r="U26" s="3" t="inlineStr"/>
-      <c r="V26" s="3" t="n">
-        <v>16.6</v>
-      </c>
       <c r="W26" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="X26" s="3" t="inlineStr"/>
-      <c r="Y26" s="3" t="inlineStr"/>
-      <c r="Z26" s="3" t="inlineStr"/>
+        <v>16.2</v>
+      </c>
+      <c r="X26" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>2.6</v>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2180,50 +2668,78 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="n">
+        <v>2305.9</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>15.8</v>
+      </c>
       <c r="F27" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>14.9</v>
+      </c>
       <c r="I27" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>21.9</v>
+      </c>
       <c r="K27" s="3" t="n">
-        <v>3.9</v>
+        <v>10.8</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="M27" s="3" t="inlineStr"/>
+        <v>15.4</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>14.8</v>
+      </c>
       <c r="N27" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S27" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X27" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y27" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z27" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="O27" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q27" s="3" t="inlineStr"/>
-      <c r="R27" s="3" t="inlineStr"/>
-      <c r="S27" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="T27" s="3" t="n">
-        <v>173</v>
-      </c>
-      <c r="U27" s="3" t="inlineStr"/>
-      <c r="V27" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="W27" s="3" t="inlineStr"/>
-      <c r="X27" s="3" t="inlineStr"/>
-      <c r="Y27" s="3" t="inlineStr"/>
-      <c r="Z27" s="3" t="inlineStr"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2237,50 +2753,78 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="n">
+        <v>2023.9</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>21.9</v>
+      </c>
       <c r="E28" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="3" t="inlineStr"/>
+        <v>13.8</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>22.8</v>
+      </c>
       <c r="I28" s="3" t="n">
-        <v>24.2</v>
+        <v>0.9</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="L28" s="3" t="inlineStr"/>
-      <c r="M28" s="3" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="K28" s="8" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>14.2</v>
+      </c>
       <c r="N28" s="3" t="n">
-        <v>16.5</v>
+        <v>4.4</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Q28" s="3" t="inlineStr"/>
-      <c r="R28" s="3" t="inlineStr"/>
+        <v>18.8</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>17</v>
+      </c>
       <c r="S28" s="3" t="n">
-        <v>19.9</v>
+        <v>17.2</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="U28" s="3" t="inlineStr"/>
-      <c r="V28" s="3" t="inlineStr"/>
-      <c r="W28" s="3" t="inlineStr"/>
-      <c r="X28" s="3" t="inlineStr"/>
-      <c r="Y28" s="3" t="inlineStr"/>
-      <c r="Z28" s="3" t="inlineStr"/>
+        <v>72.8</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>3.2</v>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2295,47 +2839,77 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>305.9</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr"/>
+        <v>289.8</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>17.6</v>
+      </c>
       <c r="G29" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="H29" s="8" t="n">
-        <v>82.8</v>
+        <v>2.1</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="J29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="K29" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="L29" s="3" t="inlineStr"/>
-      <c r="M29" s="3" t="inlineStr"/>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>14.4</v>
+      </c>
       <c r="N29" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="P29" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="O29" s="3" t="n">
-        <v>195</v>
-      </c>
-      <c r="P29" s="3" t="inlineStr"/>
-      <c r="Q29" s="3" t="inlineStr"/>
-      <c r="R29" s="3" t="inlineStr"/>
-      <c r="S29" s="3" t="inlineStr"/>
+      <c r="Q29" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="T29" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="U29" s="3" t="inlineStr"/>
-      <c r="V29" s="3" t="inlineStr"/>
-      <c r="W29" s="3" t="inlineStr"/>
-      <c r="X29" s="3" t="inlineStr"/>
-      <c r="Y29" s="3" t="inlineStr"/>
-      <c r="Z29" s="3" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="Y29" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="Z29" s="3" t="n">
+        <v>3.2</v>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -2350,51 +2924,77 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>289.8</v>
+        <v>1682.9</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>121.9</v>
-      </c>
-      <c r="E30" s="3" t="inlineStr"/>
-      <c r="F30" s="3" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
+        <v>1120.9</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>43.7</v>
+      </c>
       <c r="H30" s="3" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>456.6</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>20021.4</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>561.9</v>
+      </c>
+      <c r="U30" s="3" t="n">
+        <v>394.6</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="W30" s="3" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="X30" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="I30" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" s="3" t="inlineStr"/>
-      <c r="L30" s="3" t="n">
-        <v>114.8</v>
-      </c>
-      <c r="M30" s="3" t="inlineStr"/>
-      <c r="N30" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O30" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="P30" s="3" t="inlineStr"/>
-      <c r="Q30" s="3" t="inlineStr"/>
-      <c r="R30" s="3" t="inlineStr"/>
-      <c r="S30" s="3" t="inlineStr"/>
-      <c r="T30" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="U30" s="3" t="inlineStr"/>
-      <c r="V30" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="W30" s="3" t="inlineStr"/>
-      <c r="X30" s="3" t="n">
-        <v>182200.9</v>
-      </c>
-      <c r="Y30" s="3" t="inlineStr"/>
-      <c r="Z30" s="3" t="inlineStr"/>
+      <c r="Y30" s="3" t="n">
+        <v>441.8</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>112.2</v>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2409,70 +3009,76 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1609.9</v>
-      </c>
-      <c r="D31" s="8" t="n">
-        <v>12.9</v>
+        <v>322</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>36</v>
+        <v>13.7</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>18.1</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>4.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>22.8</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>9.4</v>
+        <v>1.8</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="3" t="inlineStr"/>
-      <c r="N31" s="3" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="O31" s="3" t="n">
-        <v>42034.4</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q31" s="8" t="n">
-        <v>5.4</v>
+        <v>1</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>18.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>361.1</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="V31" s="8" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="Y31" s="3" t="n">
         <v>88.8</v>
       </c>
-      <c r="W31" s="3" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="Y31" s="3" t="n">
-        <v>9491</v>
-      </c>
       <c r="Z31" s="3" t="n">
-        <v>7.1</v>
+        <v>941.6</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -2488,57 +3094,77 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>322</v>
-      </c>
-      <c r="D32" s="3" t="inlineStr"/>
+        <v>482.8</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>24.9</v>
+      </c>
       <c r="E32" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>18.1</v>
+        <v>1.4</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>11.9</v>
       </c>
       <c r="G32" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J32" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="H32" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="K32" s="3" t="inlineStr"/>
-      <c r="L32" s="3" t="inlineStr"/>
-      <c r="M32" s="3" t="inlineStr"/>
+      <c r="K32" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>14.9</v>
+      </c>
       <c r="N32" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O32" s="3" t="inlineStr"/>
+        <v>16.8</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>895</v>
+      </c>
       <c r="P32" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q32" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="Q32" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="S32" s="3" t="inlineStr"/>
-      <c r="T32" s="3" t="inlineStr"/>
-      <c r="U32" s="8" t="n">
-        <v>81</v>
+      <c r="R32" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>901.1</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="W32" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X32" s="3" t="inlineStr"/>
-      <c r="Y32" s="3" t="inlineStr"/>
-      <c r="Z32" s="3" t="inlineStr"/>
+        <v>14.9</v>
+      </c>
+      <c r="W32" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -2552,57 +3178,77 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="n">
-        <v>8.9</v>
+      <c r="C33" s="3" t="n">
+        <v>482.8</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>11.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>12.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I33" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="P33" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K33" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="L33" s="3" t="inlineStr"/>
-      <c r="M33" s="3" t="inlineStr"/>
-      <c r="N33" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="O33" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="P33" s="3" t="inlineStr"/>
-      <c r="Q33" s="8" t="n">
-        <v>17</v>
+      <c r="Q33" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>158.1</v>
-      </c>
-      <c r="S33" s="8" t="n">
-        <v>11.8</v>
+        <v>16.8</v>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V33" s="3" t="inlineStr"/>
-      <c r="W33" s="3" t="inlineStr"/>
-      <c r="X33" s="3" t="inlineStr"/>
+        <v>31.9</v>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W33" s="8" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="X33" s="8" t="n">
+        <v>40.6</v>
+      </c>
       <c r="Y33" s="3" t="n">
-        <v>195</v>
+        <v>71.8</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -2617,49 +3263,77 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="3" t="inlineStr"/>
+      <c r="C34" s="3" t="n">
+        <v>492.8</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>25</v>
+      </c>
       <c r="E34" s="8" t="n">
-        <v>11.5</v>
+        <v>113.6</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>17.9</v>
+        <v>11.9</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>19.7</v>
+        <v>12.6</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="I34" s="3" t="inlineStr"/>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>23.1</v>
+      </c>
       <c r="J34" s="3" t="n">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="K34" s="3" t="inlineStr"/>
-      <c r="L34" s="3" t="inlineStr"/>
-      <c r="M34" s="3" t="inlineStr"/>
-      <c r="N34" s="3" t="inlineStr"/>
+        <v>3.9</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O34" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="P34" s="3" t="inlineStr"/>
-      <c r="Q34" s="3" t="inlineStr"/>
-      <c r="R34" s="3" t="inlineStr"/>
-      <c r="S34" s="3" t="inlineStr"/>
+        <v>92</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="Q34" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="T34" s="3" t="n">
-        <v>121.9</v>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V34" s="3" t="inlineStr"/>
-      <c r="W34" s="3" t="inlineStr"/>
-      <c r="X34" s="3" t="inlineStr"/>
+        <v>26.8</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="V34" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W34" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X34" s="8" t="n">
+        <v>16.7</v>
+      </c>
       <c r="Y34" s="3" t="n">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>4.8</v>
+        <v>89.2</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -2674,47 +3348,77 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>11</v>
+      </c>
       <c r="E35" s="8" t="n">
-        <v>11.5</v>
+        <v>13.6</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>19.3</v>
+        <v>13.3</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H35" s="8" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr"/>
+        <v>89.40000000000001</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="J35" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L35" s="3" t="inlineStr"/>
-      <c r="M35" s="3" t="inlineStr"/>
-      <c r="N35" s="3" t="inlineStr"/>
+      <c r="L35" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="M35" s="8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="O35" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="P35" s="3" t="inlineStr"/>
-      <c r="Q35" s="3" t="inlineStr"/>
-      <c r="R35" s="3" t="inlineStr"/>
-      <c r="S35" s="3" t="inlineStr"/>
+        <v>9180</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q35" s="8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="S35" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="T35" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U35" s="3" t="inlineStr"/>
-      <c r="V35" s="3" t="inlineStr"/>
-      <c r="W35" s="3" t="inlineStr"/>
-      <c r="X35" s="3" t="inlineStr"/>
-      <c r="Y35" s="3" t="inlineStr"/>
+        <v>600.8</v>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v>1424.8</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="W35" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>75.5</v>
+      </c>
       <c r="Z35" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -2729,45 +3433,75 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="3" t="inlineStr"/>
-      <c r="E36" s="3" t="inlineStr"/>
+      <c r="C36" s="3" t="n">
+        <v>498.3</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>13.9</v>
+      </c>
       <c r="F36" s="3" t="n">
-        <v>19.1</v>
+        <v>12.1</v>
       </c>
       <c r="G36" s="8" t="n">
         <v>10.3</v>
       </c>
-      <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>2.3</v>
+      </c>
       <c r="J36" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L36" s="3" t="inlineStr"/>
-      <c r="M36" s="8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="N36" s="3" t="inlineStr"/>
-      <c r="O36" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>91</v>
+      </c>
       <c r="P36" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q36" s="3" t="inlineStr"/>
-      <c r="R36" s="3" t="inlineStr"/>
-      <c r="S36" s="3" t="inlineStr"/>
+      <c r="Q36" s="8" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S36" s="8" t="n">
+        <v>71</v>
+      </c>
       <c r="T36" s="3" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="U36" s="3" t="inlineStr"/>
+        <v>552.1</v>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v>1424.8</v>
+      </c>
       <c r="V36" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="W36" s="3" t="inlineStr"/>
-      <c r="X36" s="3" t="inlineStr"/>
-      <c r="Y36" s="3" t="inlineStr"/>
+      <c r="W36" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>79.8</v>
+      </c>
       <c r="Z36" s="3" t="n">
         <v>4.5</v>
       </c>
@@ -2785,61 +3519,73 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1182.8</v>
+        <v>122.8</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>112.2</v>
-      </c>
-      <c r="E37" s="3" t="inlineStr"/>
+        <v>124.2</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>825.8</v>
+      </c>
       <c r="F37" s="3" t="n">
-        <v>928.6</v>
+        <v>22.6</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H37" s="3" t="inlineStr"/>
+        <v>22.9</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="I37" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr"/>
-      <c r="K37" s="3" t="inlineStr"/>
+        <v>110.8</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>122.9</v>
+      </c>
       <c r="L37" s="3" t="n">
-        <v>1.3</v>
+        <v>29.1</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N37" s="3" t="inlineStr"/>
+        <v>8012</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>19.1</v>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>9449</v>
+        <v>449</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Q37" s="3" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>113.4</v>
+      </c>
       <c r="R37" s="3" t="n">
-        <v>81.8</v>
+        <v>1</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>284.8</v>
+        <v>84.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>312.4</v>
+        <v>313.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>24.8</v>
+        <v>25.8</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>1291</v>
+        <v>21</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>50.4</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>85.2</v>
+        <v>82</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>909.2</v>
+        <v>940.2</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>128.1</v>
@@ -2860,51 +3606,75 @@
       <c r="C38" s="3" t="n">
         <v>9438.6</v>
       </c>
-      <c r="D38" s="3" t="inlineStr"/>
-      <c r="E38" s="3" t="inlineStr"/>
+      <c r="D38" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="F38" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G38" s="3" t="inlineStr"/>
+        <v>18.5</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>10.5</v>
+      </c>
       <c r="H38" s="3" t="n">
-        <v>12.8</v>
+        <v>12.3</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="3" t="n">
-        <v>45.4</v>
+        <v>23.2</v>
+      </c>
+      <c r="K38" s="8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="L38" s="8" t="n">
+        <v>15.1</v>
       </c>
       <c r="M38" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="N38" s="3" t="inlineStr"/>
+      <c r="N38" s="8" t="n">
+        <v>52.1</v>
+      </c>
       <c r="O38" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="Q38" s="3" t="n">
+        <v>22.7</v>
+      </c>
       <c r="R38" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="S38" s="3" t="inlineStr"/>
-      <c r="T38" s="3" t="inlineStr"/>
-      <c r="U38" s="3" t="inlineStr"/>
+        <v>17.4</v>
+      </c>
+      <c r="S38" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>11</v>
+      </c>
       <c r="V38" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>464.1</v>
-      </c>
-      <c r="X38" s="3" t="inlineStr"/>
-      <c r="Y38" s="3" t="inlineStr"/>
-      <c r="Z38" s="3" t="inlineStr"/>
+        <v>16.1</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="Y38" s="3" t="n">
+        <v>224.9</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2919,55 +3689,77 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1395.3</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F39" s="8" t="n">
+        <v>395</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>92</v>
+      </c>
+      <c r="F39" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="G39" s="8" t="n">
         <v>11.8</v>
       </c>
-      <c r="H39" s="8" t="n">
-        <v>12.8</v>
+      <c r="H39" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr"/>
-      <c r="K39" s="3" t="inlineStr"/>
-      <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="3" t="inlineStr"/>
-      <c r="N39" s="3" t="inlineStr"/>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>52.1</v>
+      </c>
       <c r="O39" s="3" t="n">
         <v>91</v>
       </c>
       <c r="P39" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="S39" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="T39" s="3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v>71</v>
+      </c>
+      <c r="W39" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="Y39" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="Q39" s="3" t="inlineStr"/>
-      <c r="R39" s="3" t="inlineStr"/>
-      <c r="S39" s="3" t="inlineStr"/>
-      <c r="T39" s="3" t="n">
-        <v>520.8</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="W39" s="3" t="inlineStr"/>
-      <c r="X39" s="3" t="inlineStr"/>
-      <c r="Y39" s="3" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="Z39" s="3" t="inlineStr"/>
+      <c r="Z39" s="3" t="n">
+        <v>16.4</v>
+      </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -2982,44 +3774,74 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>4034.4</v>
-      </c>
-      <c r="D40" s="3" t="inlineStr"/>
-      <c r="E40" s="3" t="inlineStr"/>
+        <v>2942.1</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>12.8</v>
+      </c>
       <c r="F40" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="3" t="inlineStr"/>
-      <c r="I40" s="3" t="n">
-        <v>3</v>
+      <c r="G40" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>1.6</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="K40" s="3" t="inlineStr"/>
-      <c r="L40" s="3" t="inlineStr"/>
-      <c r="M40" s="3" t="inlineStr"/>
-      <c r="N40" s="3" t="inlineStr"/>
+      <c r="L40" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="M40" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>19.4</v>
+      </c>
       <c r="O40" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P40" s="3" t="inlineStr"/>
-      <c r="Q40" s="3" t="inlineStr"/>
-      <c r="R40" s="3" t="inlineStr"/>
-      <c r="S40" s="3" t="inlineStr"/>
-      <c r="T40" s="3" t="inlineStr"/>
-      <c r="U40" s="8" t="n">
+        <v>299.5</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="T40" s="3" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="U40" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V40" s="8" t="n">
+      <c r="V40" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="W40" s="3" t="inlineStr"/>
-      <c r="X40" s="3" t="inlineStr"/>
-      <c r="Y40" s="3" t="inlineStr"/>
+      <c r="W40" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="Y40" s="3" t="n">
+        <v>72</v>
+      </c>
       <c r="Z40" s="3" t="n">
-        <v>16.2</v>
+        <v>6.2</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3035,52 +3857,74 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>340.1</v>
-      </c>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="n">
-        <v>2.2</v>
+        <v>408.4</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I41" s="8" t="n">
+        <v>11.1</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K41" s="3" t="inlineStr"/>
+        <v>4.7</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L41" s="3" t="n">
-        <v>69.8</v>
+        <v>14.8</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" s="3" t="inlineStr"/>
-      <c r="R41" s="3" t="inlineStr"/>
-      <c r="S41" s="3" t="inlineStr"/>
-      <c r="T41" s="3" t="inlineStr"/>
+      <c r="Q41" s="8" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>162.5</v>
+      </c>
       <c r="U41" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="W41" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X41" s="3" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="W41" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="Y41" s="3" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3096,50 +3940,70 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1337</v>
-      </c>
-      <c r="D42" s="3" t="inlineStr"/>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="3" t="inlineStr"/>
+        <v>349.1</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="3" t="inlineStr"/>
-      <c r="I42" s="3" t="n">
-        <v>1.7</v>
-      </c>
+      <c r="H42" s="8" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="I42" s="3" t="inlineStr"/>
       <c r="J42" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K42" s="3" t="inlineStr"/>
+      <c r="K42" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L42" s="3" t="n">
-        <v>10.4</v>
+        <v>11.4</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="N42" s="3" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>14.6</v>
+      </c>
       <c r="O42" s="3" t="n">
-        <v>82</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" s="3" t="inlineStr"/>
-      <c r="R42" s="3" t="inlineStr"/>
-      <c r="S42" s="3" t="inlineStr"/>
-      <c r="T42" s="3" t="inlineStr"/>
+      <c r="Q42" s="3" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S42" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>1460.5</v>
+      </c>
       <c r="U42" s="3" t="n">
-        <v>142.4</v>
-      </c>
-      <c r="V42" s="3" t="inlineStr"/>
+        <v>10.4</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="W42" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="n">
-        <v>81.8</v>
+        <v>87</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>98.7</v>
+        <v>2.6</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3155,52 +4019,74 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1653.1</v>
-      </c>
-      <c r="D43" s="3" t="inlineStr"/>
+        <v>517</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="E43" s="3" t="inlineStr"/>
       <c r="F43" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="3" t="inlineStr"/>
-      <c r="I43" s="3" t="inlineStr"/>
+        <v>18.1</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>19.7</v>
+      </c>
       <c r="J43" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K43" s="3" t="inlineStr"/>
+        <v>21.1</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L43" s="3" t="n">
-        <v>1.4</v>
+        <v>16.2</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="N43" s="3" t="inlineStr"/>
+        <v>4.4</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>16.9</v>
+      </c>
       <c r="O43" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="3" t="inlineStr"/>
-      <c r="R43" s="3" t="n">
-        <v>18.7</v>
+        <v>82</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="R43" s="8" t="n">
+        <v>16.5</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>12.9</v>
+        <v>15.6</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>959.3</v>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="V43" s="3" t="inlineStr"/>
-      <c r="W43" s="3" t="inlineStr"/>
-      <c r="X43" s="3" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>16.2</v>
+      </c>
       <c r="Y43" s="3" t="n">
-        <v>78</v>
+        <v>81.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>85</v>
+        <v>3.7</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -3216,18 +4102,24 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>22830.1</v>
-      </c>
-      <c r="D44" s="8" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="E44" s="3" t="inlineStr"/>
+        <v>653.1</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>12.6</v>
+      </c>
       <c r="F44" s="3" t="n">
         <v>18</v>
       </c>
       <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="3" t="inlineStr"/>
-      <c r="I44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>2.6</v>
+      </c>
       <c r="J44" s="3" t="n">
         <v>5</v>
       </c>
@@ -3235,7 +4127,7 @@
         <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>1.4</v>
+        <v>13.6</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>12.6</v>
@@ -3244,33 +4136,29 @@
       <c r="O44" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="3" t="inlineStr"/>
-      <c r="R44" s="3" t="n">
-        <v>18.7</v>
+      <c r="P44" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Q44" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="R44" s="8" t="n">
+        <v>68.09999999999999</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>12.9</v>
+        <v>13.9</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>959.3</v>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="V44" s="3" t="inlineStr"/>
-      <c r="W44" s="3" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="Y44" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="Z44" s="3" t="n">
-        <v>28.7</v>
-      </c>
+        <v>59.5</v>
+      </c>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -3285,54 +4173,76 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>22830.1</v>
+        <v>2283</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>191.7</v>
-      </c>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr"/>
+        <v>198.5</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>219.1</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>110.2</v>
+      </c>
       <c r="G45" s="3" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>10.8</v>
+        <v>128.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>15.2</v>
+        <v>13.2</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>126.2</v>
+        <v>26.2</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="3" t="inlineStr"/>
-      <c r="N45" s="3" t="inlineStr"/>
+        <v>10.1</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>91.8</v>
+      </c>
       <c r="O45" s="3" t="n">
-        <v>240.9</v>
-      </c>
-      <c r="P45" s="3" t="inlineStr"/>
-      <c r="Q45" s="3" t="inlineStr"/>
-      <c r="R45" s="3" t="inlineStr"/>
+        <v>290.9</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="Q45" s="3" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>104.1</v>
+      </c>
       <c r="S45" s="3" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="T45" s="3" t="inlineStr"/>
-      <c r="U45" s="3" t="inlineStr"/>
+        <v>99.8</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>381</v>
+      </c>
+      <c r="U45" s="3" t="n">
+        <v>169</v>
+      </c>
       <c r="V45" s="3" t="n">
         <v>111.8</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>95.8</v>
+        <v>220.8</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="Y45" s="3" t="inlineStr"/>
+        <v>89.59999999999999</v>
+      </c>
+      <c r="Y45" s="3" t="n">
+        <v>4648.4</v>
+      </c>
       <c r="Z45" s="3" t="n">
-        <v>28.7</v>
+        <v>28.1</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -3348,57 +4258,77 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>29497</v>
-      </c>
-      <c r="D46" s="8" t="n">
+        <v>498</v>
+      </c>
+      <c r="D46" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>4.4</v>
+        <v>13.3</v>
       </c>
       <c r="F46" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="G46" s="8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H46" s="8" t="n">
+      <c r="G46" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H46" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>22.8</v>
+        <v>2.5</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
+        <v>4.4</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>4.6</v>
+      </c>
       <c r="L46" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="M46" s="3" t="inlineStr"/>
-      <c r="N46" s="3" t="inlineStr"/>
-      <c r="O46" s="3" t="inlineStr"/>
+      <c r="M46" s="8" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="N46" s="8" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>254.1</v>
+      </c>
       <c r="P46" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="n">
+        <v>22.8</v>
+      </c>
       <c r="R46" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v>14.2</v>
+      </c>
       <c r="V46" s="3" t="n">
-        <v>212.6</v>
-      </c>
-      <c r="W46" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="W46" s="8" t="n">
         <v>15.9</v>
       </c>
-      <c r="X46" s="3" t="inlineStr"/>
-      <c r="Y46" s="3" t="inlineStr"/>
-      <c r="Z46" s="3" t="inlineStr"/>
+      <c r="X46" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_decimal_place_correction.xlsx
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>582.9</v>
+        <v>582.2</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>25.1</v>
+        <v>8.4</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>13.6</v>
@@ -754,13 +754,13 @@
         <v>13.1</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>45.1</v>
+        <v>2.8</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>14.2</v>
+        <v>1.2</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>11.7</v>
@@ -769,7 +769,7 @@
         <v>13.1</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>87</v>
@@ -787,16 +787,14 @@
         <v>16.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>152</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v>120.7</v>
+        <v>52</v>
+      </c>
+      <c r="U4" s="3" t="inlineStr"/>
+      <c r="V4" s="3" t="n">
+        <v>107.1</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
@@ -815,10 +813,10 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>288.9</v>
+        <v>388.5</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>10.8</v>
+        <v>29.1</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>14.2</v>
@@ -829,32 +827,32 @@
       <c r="G5" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="H5" s="8" t="n">
-        <v>12.3</v>
+      <c r="H5" s="3" t="n">
+        <v>12.1</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>12.7</v>
+        <v>0.8</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.4</v>
+        <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>16.1</v>
+        <v>18.9</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>19.4</v>
+        <v>18.9</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>22.4</v>
@@ -881,7 +879,7 @@
         <v>18.4</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>75.5</v>
+        <v>7.5</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>6</v>
@@ -908,8 +906,8 @@
       <c r="E6" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="F6" s="8" t="n">
-        <v>18</v>
+      <c r="F6" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>11.2</v>
@@ -926,14 +924,14 @@
       <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="8" t="n">
+      <c r="L6" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="M6" s="3" t="n">
-        <v>13</v>
+      <c r="M6" s="8" t="n">
+        <v>30.9</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>1.9</v>
+        <v>19.5</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>92</v>
@@ -942,7 +940,7 @@
         <v>1.2</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>25.6</v>
+        <v>23.6</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>17.9</v>
@@ -959,17 +957,17 @@
       <c r="V6" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="W6" s="8" t="n">
+      <c r="W6" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X6" s="8" t="n">
-        <v>18.1</v>
+      <c r="X6" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>87</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -990,69 +988,67 @@
       <c r="D7" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="E7" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>189.8</v>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>10.7</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="8" t="n">
         <v>12</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.4</v>
+        <v>11.4</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>3.4</v>
+        <v>8.4</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="M7" s="8" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>18.8</v>
+      <c r="M7" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>52.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>593</v>
+        <v>293</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q7" s="3" t="inlineStr"/>
       <c r="R7" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>59.1</v>
       </c>
-      <c r="U7" s="8" t="n">
+      <c r="U7" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="W7" s="8" t="n">
+      <c r="W7" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="X7" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.1</v>
+        <v>21</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1071,7 +1067,7 @@
         <v>229.8</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>41.9</v>
+        <v>21.9</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>13.8</v>
@@ -1092,7 +1088,7 @@
         <v>1.8</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>27.2</v>
+        <v>6.4</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>15.1</v>
@@ -1101,10 +1097,10 @@
         <v>14.2</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.8</v>
@@ -1115,14 +1111,14 @@
       <c r="R8" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="S8" s="8" t="n">
+      <c r="S8" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>76</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>3.8</v>
+        <v>35.8</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>17.1</v>
@@ -1153,67 +1149,65 @@
         <v>118.5</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>61.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>93.09999999999999</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>881.5</v>
+        <v>20.9</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>10.5</v>
-      </c>
+        <v>63.1</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="n">
-        <v>16.9</v>
+        <v>260.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>31.1</v>
+        <v>51.1</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>19.4</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>60.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>86</v>
+        <v>16.6</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>959</v>
+        <v>1590.1</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1194</v>
+        <v>114</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>88.09999999999999</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>6.8</v>
+        <v>86.8</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>2162.6</v>
+        <v>212.6</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>22</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>959</v>
+        <v>94</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>89.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>419.8</v>
+        <v>848.1</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>2</v>
@@ -1232,7 +1226,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>449</v>
+        <v>495</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>23.7</v>
@@ -1240,7 +1234,7 @@
       <c r="E10" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="G10" s="3" t="n">
@@ -1250,12 +1244,14 @@
         <v>12.6</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
+        <v>3.8</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>14.7</v>
       </c>
@@ -1266,22 +1262,22 @@
         <v>15.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>91.8</v>
+        <v>921.8</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>1.3</v>
+        <v>113.8</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>85.8</v>
+        <v>9</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="S10" s="3" t="n">
-        <v>17.2</v>
+      <c r="S10" s="8" t="n">
+        <v>78.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>62.9</v>
+        <v>62.8</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>10.6</v>
@@ -1315,58 +1311,58 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>221.8</v>
+        <v>924.2</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>22.5</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F11" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F11" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="K11" s="8" t="n">
-        <v>10.8</v>
+      <c r="K11" s="3" t="n">
+        <v>10.2</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>14</v>
+        <v>14.8</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>11.8</v>
+        <v>18.1</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="P11" s="8" t="n">
-        <v>10.4</v>
+        <v>885</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="S11" s="8" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="S11" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>28.4</v>
+        <v>82</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>10.6</v>
@@ -1410,7 +1406,7 @@
         <v>17.9</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>9.1</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>13</v>
@@ -1425,16 +1421,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>11.4</v>
+        <v>14.5</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>83.5</v>
+        <v>38.5</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>12</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>92.8</v>
+        <v>12.8</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.2</v>
@@ -1455,7 +1451,7 @@
         <v>6.2</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>16</v>
+        <v>1.6</v>
       </c>
       <c r="W12" s="3" t="n">
         <v>14.8</v>
@@ -1464,7 +1460,7 @@
         <v>17.5</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>240.8</v>
+        <v>18.4</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>3.8</v>
@@ -1491,14 +1487,14 @@
       <c r="E13" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="F13" s="8" t="n">
-        <v>18.8</v>
+      <c r="F13" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>28.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>15.1</v>
+        <v>13.1</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.4</v>
@@ -1510,7 +1506,7 @@
         <v>15.7</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>14.4</v>
@@ -1522,7 +1518,7 @@
         <v>94.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="Q13" s="8" t="n">
         <v>15.8</v>
@@ -1531,10 +1527,10 @@
         <v>14.8</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>1.6</v>
+        <v>16.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>90.5</v>
+        <v>20.5</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>6.2</v>
@@ -1546,10 +1542,10 @@
         <v>15.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>15.1</v>
+        <v>1.5</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>2.8</v>
@@ -1573,26 +1569,26 @@
       <c r="D14" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="8" t="n">
         <v>13.4</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>17.8</v>
+        <v>11.4</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>12.5</v>
+        <v>71.5</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>21.4</v>
+        <v>11.8</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>26.8</v>
+        <v>86.8</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>14.4</v>
@@ -1610,22 +1606,22 @@
         <v>1</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>21.3</v>
+        <v>2.8</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>18.1</v>
+        <v>1.8</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>7.2</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>14.8</v>
@@ -1660,10 +1656,10 @@
         <v>13.2</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>78.3</v>
+        <v>7.5</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>12.6</v>
@@ -1672,7 +1668,7 @@
         <v>1.2</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>5.9</v>
@@ -1681,7 +1677,7 @@
         <v>14.2</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>148.1</v>
+        <v>13.8</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>15.5</v>
@@ -1690,7 +1686,7 @@
         <v>96.8</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>19.8</v>
@@ -1736,73 +1732,73 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1972.2</v>
+        <v>1973.2</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>114.8</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7.4</v>
+        <v>27.4</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>47.4</v>
+        <v>17.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>649.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>5.9</v>
+        <v>1.2</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>6.9</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>191.2</v>
+        <v>73.2</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>69.40000000000001</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1164.2</v>
+        <v>15.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>64.8</v>
+        <v>4.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>96.90000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>83.8</v>
+        <v>61.4</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>164.8</v>
+        <v>3945.2</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>84.5</v>
+        <v>84</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>180.6</v>
+        <v>18.6</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>85.09999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>488.8</v>
+        <v>428.8</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>2.8</v>
@@ -1821,19 +1817,19 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>225</v>
+        <v>1469.4</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>41.8</v>
+        <v>13.8</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>4.8</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>9.5</v>
+        <v>0.9</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.9</v>
@@ -1841,11 +1837,11 @@
       <c r="I17" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J17" s="8" t="n">
+      <c r="J17" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>14.6</v>
@@ -1854,7 +1850,7 @@
         <v>13.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>19.8</v>
+        <v>15.8</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>92.90000000000001</v>
@@ -1866,16 +1862,16 @@
         <v>19.8</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>18.9</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>16.9</v>
@@ -1909,37 +1905,37 @@
         <v>428.8</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2.4</v>
+        <v>24.9</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>16.2</v>
+        <v>12.8</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>12.4</v>
+        <v>0.1</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>10.1</v>
+        <v>2.2</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.6</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>14</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>14.4</v>
+        <v>19.4</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>91</v>
@@ -1948,7 +1944,7 @@
         <v>1.4</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>21.8</v>
+        <v>64.5</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>17.8</v>
@@ -1963,13 +1959,13 @@
         <v>8</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>16.9</v>
+        <v>18.2</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>16.8</v>
+        <v>16</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>81.8</v>
@@ -1991,10 +1987,10 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>840.6</v>
+        <v>440.6</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1.5</v>
+        <v>22</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>14</v>
@@ -2003,13 +1999,13 @@
         <v>19.5</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="H19" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>3.4</v>
@@ -2024,7 +2020,7 @@
         <v>1.4</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>11.5</v>
+        <v>46.4</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>92</v>
@@ -2033,7 +2029,7 @@
         <v>11.4</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>24.9</v>
+        <v>2.4</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>18.1</v>
@@ -2044,21 +2040,23 @@
       <c r="T19" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="U19" s="8" t="n">
+      <c r="U19" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V19" s="3" t="inlineStr"/>
+      <c r="V19" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="W19" s="3" t="n">
-        <v>16.8</v>
+        <v>4.9</v>
       </c>
       <c r="X19" s="8" t="n">
-        <v>18.8</v>
+        <v>185.3</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>81</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>27.4</v>
+        <v>127.4</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2077,22 +2075,22 @@
         <v>153.1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>24.9</v>
+        <v>21.9</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>17.8</v>
+        <v>1.7</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>3.4</v>
@@ -2116,10 +2114,10 @@
         <v>0.5</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>20.6</v>
+        <v>2</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>17.6</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>18.5</v>
@@ -2128,13 +2126,13 @@
         <v>76.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>5.7</v>
+        <v>14.4</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>16.8</v>
+        <v>75.5</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>18.6</v>
@@ -2168,31 +2166,31 @@
         <v>14.7</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1.8</v>
+        <v>18.3</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>11.9</v>
+        <v>7.2</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="L21" s="3" t="n">
-        <v>16.4</v>
+      <c r="L21" s="8" t="n">
+        <v>56.2</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1</v>
+        <v>121.3</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>90.8</v>
@@ -2200,22 +2198,22 @@
       <c r="P21" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q21" s="8" t="n">
-        <v>21.5</v>
+      <c r="Q21" s="3" t="n">
+        <v>21.4</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>18.9</v>
+        <v>43.1</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>74</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="V21" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="V21" s="8" t="n">
         <v>18.2</v>
       </c>
       <c r="W21" s="3" t="n">
@@ -2246,41 +2244,41 @@
       <c r="C22" s="3" t="n">
         <v>123.3</v>
       </c>
-      <c r="D22" s="8" t="n">
-        <v>120.6</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>94.40000000000001</v>
+      <c r="D22" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H22" s="8" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H22" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="N22" s="3" t="n">
-        <v>11.6</v>
+      <c r="N22" s="8" t="n">
+        <v>68.90000000000001</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>1.8</v>
@@ -2295,13 +2293,13 @@
         <v>17.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>74</v>
+        <v>740.8</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>6.2</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>16.9</v>
@@ -2313,7 +2311,7 @@
         <v>94.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2329,43 +2327,43 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1921.2</v>
+        <v>477.4</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>11153.1</v>
+        <v>113.1</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>49.4</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>940.8</v>
+        <v>91</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>43.1</v>
+        <v>2654</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>69.8</v>
+        <v>636.4</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>80.8</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>38.2</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>16.1</v>
+        <v>161.4</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>122.1</v>
+        <v>14.6</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>816.4</v>
+        <v>31.6</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>1</v>
@@ -2377,7 +2375,7 @@
         <v>88.8</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>90</v>
+        <v>90.2</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>347.9</v>
@@ -2386,19 +2384,19 @@
         <v>40.6</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>918.9</v>
+        <v>919.8</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>911.8</v>
+        <v>942.1</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>48.4</v>
+        <v>148.8</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>113.8</v>
+        <v>13.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2429,7 +2427,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>69.8</v>
+        <v>636.4</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>1.5</v>
@@ -2441,13 +2439,13 @@
         <v>38.2</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>15.2</v>
+        <v>45.9</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>92.40000000000001</v>
@@ -2465,7 +2463,7 @@
         <v>18.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>69.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>8.1</v>
@@ -2473,11 +2471,11 @@
       <c r="V24" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>87.09999999999999</v>
@@ -2499,40 +2497,40 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>490.4</v>
-      </c>
-      <c r="D25" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>13.6</v>
+        <v>130.4</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>643.1</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>15</v>
+        <v>18.8</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="H25" s="8" t="n">
-        <v>12.8</v>
+      <c r="H25" s="3" t="n">
+        <v>12.9</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="J25" s="8" t="n">
-        <v>18.1</v>
+      <c r="J25" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>19.1</v>
+        <v>15.1</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>849.2</v>
+        <v>34.2</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>15.4</v>
+        <v>1.1</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>910.8</v>
@@ -2540,17 +2538,17 @@
       <c r="P25" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="Q25" s="8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>11.6</v>
+      <c r="Q25" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="S25" s="8" t="n">
+        <v>17.6</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="U25" s="3" t="n">
         <v>8</v>
@@ -2558,8 +2556,8 @@
       <c r="V25" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W25" s="8" t="n">
-        <v>12.9</v>
+      <c r="W25" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>18.1</v>
@@ -2584,7 +2582,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>287.8</v>
+        <v>87.8</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>23.5</v>
@@ -2599,19 +2597,19 @@
         <v>8.9</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="L26" s="8" t="n">
-        <v>84.59999999999999</v>
+        <v>5.9</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>14.9</v>
@@ -2623,10 +2621,10 @@
         <v>95</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0.8</v>
+        <v>11.4</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>28.7</v>
+        <v>20.7</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>17.3</v>
@@ -2641,19 +2639,19 @@
         <v>6.6</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>12.9</v>
+        <v>17.9</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X26" s="8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="X26" s="3" t="n">
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>88.5</v>
+        <v>2.5</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2669,16 +2667,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2305.9</v>
+        <v>5.9</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>15.8</v>
+        <v>13.8</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>18.9</v>
+        <v>14.1</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>9.1</v>
@@ -2687,22 +2685,22 @@
         <v>14.9</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>21.9</v>
+        <v>1.2</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="L27" s="8" t="n">
+      <c r="L27" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>94</v>
@@ -2716,11 +2714,11 @@
       <c r="R27" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="S27" s="8" t="n">
+      <c r="S27" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>5.6</v>
@@ -2729,7 +2727,7 @@
         <v>17.8</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>16.8</v>
+        <v>15.8</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>18.5</v>
@@ -2754,7 +2752,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2023.9</v>
+        <v>305.9</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>21.9</v>
@@ -2762,38 +2760,38 @@
       <c r="E28" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="F28" s="8" t="n">
-        <v>117.9</v>
+      <c r="F28" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>8</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>22.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K28" s="8" t="n">
-        <v>65.40000000000001</v>
+        <v>1.1</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>14.7</v>
+        <v>15.4</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>95</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>18.8</v>
+        <v>0.8</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>20.5</v>
@@ -2808,7 +2806,7 @@
         <v>72.8</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>16.7</v>
@@ -2841,44 +2839,44 @@
       <c r="C29" s="3" t="n">
         <v>289.8</v>
       </c>
-      <c r="D29" s="8" t="n">
+      <c r="D29" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>17.6</v>
+        <v>17.1</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2.1</v>
+        <v>84.5</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="L29" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="L29" s="8" t="n">
         <v>14.9</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>14.4</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>16.5</v>
+        <v>1.6</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>95</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>21.7</v>
@@ -2890,7 +2888,7 @@
         <v>18.2</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>70</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>7.8</v>
@@ -2924,13 +2922,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1682.9</v>
+        <v>1689.9</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1120.9</v>
+        <v>1129.8</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0.6</v>
+        <v>60.6</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>90.59999999999999</v>
@@ -2942,58 +2940,58 @@
         <v>80.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>9.1</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>456.6</v>
+        <v>38.6</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>71.8</v>
+        <v>1.6</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>20021.4</v>
+        <v>479.8</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>20.5</v>
+        <v>105.2</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>27.4</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>90.09999999999999</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>561.9</v>
+        <v>561.8</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>394.6</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>88</v>
+        <v>18.8</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>18.8</v>
+        <v>88</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>441.8</v>
+        <v>416.8</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>112.2</v>
+        <v>12.2</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3012,7 +3010,7 @@
         <v>322</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>22.5</v>
+        <v>2.2</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>13.7</v>
@@ -3024,7 +3022,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>22.8</v>
+        <v>28.2</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>1.3</v>
@@ -3033,16 +3031,16 @@
         <v>1.8</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.1</v>
+        <v>38.6</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>14.3</v>
+        <v>1.4</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>16.8</v>
+        <v>16.1</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>94.09999999999999</v>
@@ -3060,10 +3058,10 @@
         <v>18.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v>16.3</v>
+        <v>116.3</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>6.2</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>17.6</v>
@@ -3075,10 +3073,10 @@
         <v>17.7</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>88.8</v>
+        <v>88.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>941.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3094,67 +3092,67 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>482.8</v>
+        <v>481.8</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>1.4</v>
+        <v>19.2</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>11.9</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>12.3</v>
+        <v>12.9</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>14.9</v>
+        <v>16.1</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>105.1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>16.8</v>
+        <v>16.1</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>895</v>
+        <v>83</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="R32" s="8" t="n">
-        <v>19.8</v>
+        <v>15.8</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>901.1</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="W32" s="8" t="n">
-        <v>16.6</v>
+        <v>15.9</v>
+      </c>
+      <c r="W32" s="3" t="n">
+        <v>15.6</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>17.7</v>
@@ -3179,46 +3177,46 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>482.8</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>24.1</v>
+        <v>422.8</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>49.1</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F33" s="8" t="n">
-        <v>89.7</v>
+        <v>66184.5</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>13.5</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>11.7</v>
+        <v>91.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>20.6</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>4.9</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>12.3</v>
+        <v>12.9</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>1.2</v>
+        <v>16.1</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="N33" s="3" t="n">
-        <v>15.8</v>
+      <c r="N33" s="8" t="n">
+        <v>92.40000000000001</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>93</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>23.8</v>
@@ -3227,25 +3225,25 @@
         <v>16.8</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="U33" s="8" t="n">
+        <v>319.5</v>
+      </c>
+      <c r="U33" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>18</v>
       </c>
       <c r="W33" s="8" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="X33" s="8" t="n">
-        <v>40.6</v>
+        <v>13.4</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>71.8</v>
+        <v>71</v>
       </c>
       <c r="Z33" s="3" t="n">
         <v>4.8</v>
@@ -3266,56 +3264,56 @@
       <c r="C34" s="3" t="n">
         <v>492.8</v>
       </c>
-      <c r="D34" s="8" t="n">
+      <c r="D34" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="E34" s="8" t="n">
-        <v>113.6</v>
+      <c r="E34" s="3" t="n">
+        <v>3.6</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="H34" s="8" t="n">
-        <v>8.300000000000001</v>
+      <c r="H34" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>23.1</v>
+        <v>2.3</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>11.6</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>1.1</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>17.7</v>
+        <v>1.7</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>26.8</v>
+        <v>56.8</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>12.8</v>
@@ -3324,16 +3322,14 @@
         <v>18</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X34" s="8" t="n">
-        <v>16.7</v>
-      </c>
+        <v>15.8</v>
+      </c>
+      <c r="X34" s="3" t="inlineStr"/>
       <c r="Y34" s="3" t="n">
         <v>21</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>89.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3349,16 +3345,16 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>11</v>
+        <v>24.2</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="E35" s="8" t="n">
         <v>13.6</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>13.3</v>
+        <v>4.4</v>
       </c>
       <c r="G35" s="8" t="n">
         <v>89.40000000000001</v>
@@ -3373,45 +3369,45 @@
         <v>4</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="M35" s="8" t="n">
-        <v>13.5</v>
+      <c r="M35" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.7</v>
+        <v>17.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>9180</v>
+        <v>90</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q35" s="8" t="n">
-        <v>18.8</v>
+        <v>2</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>24.8</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>18.9</v>
+        <v>18.2</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>600.8</v>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v>1424.8</v>
+        <v>60</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X35" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X35" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="Y35" s="3" t="n">
@@ -3442,17 +3438,17 @@
       <c r="E36" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="G36" s="8" t="n">
+      <c r="F36" s="8" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="G36" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>4</v>
@@ -3466,8 +3462,8 @@
       <c r="M36" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>18.9</v>
+      <c r="N36" s="8" t="n">
+        <v>81.09999999999999</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>91</v>
@@ -3475,20 +3471,20 @@
       <c r="P36" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q36" s="8" t="n">
-        <v>124.2</v>
+      <c r="Q36" s="3" t="n">
+        <v>29.2</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="S36" s="8" t="n">
-        <v>71</v>
+      <c r="S36" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>552.1</v>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v>1424.8</v>
+        <v>55.1</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>18.4</v>
@@ -3519,76 +3515,76 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>122.8</v>
+        <v>128.1</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>124.2</v>
+        <v>12.1</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>825.8</v>
+        <v>69.8</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>22.6</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>22.9</v>
+        <v>22</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>4</v>
+        <v>18.8</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>110.8</v>
+        <v>110.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>18.6</v>
+        <v>12.6</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>122.9</v>
+        <v>121.8</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>29.1</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>8012</v>
+        <v>15.6</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>19.1</v>
+        <v>11.1</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>449</v>
+        <v>44930.3</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>113.4</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>84.8</v>
+        <v>24.8</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>313.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>25.8</v>
+        <v>24.8</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>82</v>
+        <v>83.2</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>940.2</v>
+        <v>41252.4</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>128.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3604,7 +3600,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>9438.6</v>
+        <v>438.6</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>23.8</v>
@@ -3616,34 +3612,34 @@
         <v>18.5</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>12.3</v>
+        <v>22.3</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>12.1</v>
+        <v>2.1</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="K38" s="8" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="L38" s="8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L38" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="M38" s="3" t="n">
         <v>14</v>
       </c>
       <c r="N38" s="8" t="n">
-        <v>52.1</v>
+        <v>58.1</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>89.8</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>22.7</v>
@@ -3652,10 +3648,10 @@
         <v>17.4</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>17</v>
+        <v>480.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>62.1</v>
+        <v>63.9</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>11</v>
@@ -3664,16 +3660,16 @@
         <v>18.2</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>16.1</v>
+        <v>15.1</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>224.9</v>
+        <v>21.9</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3689,40 +3685,40 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>395</v>
-      </c>
-      <c r="D39" s="8" t="n">
-        <v>64.5</v>
+        <v>2392.3</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>5.2</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>8.5</v>
+        <v>15.9</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M39" s="8" t="n">
-        <v>11.5</v>
+        <v>1.8</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>5.1</v>
       </c>
       <c r="N39" s="8" t="n">
-        <v>52.1</v>
+        <v>1.5</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>91</v>
@@ -3730,35 +3726,35 @@
       <c r="P39" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q39" s="8" t="n">
-        <v>19.6</v>
+      <c r="Q39" s="3" t="n">
+        <v>29.6</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>52.8</v>
+        <v>52</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v>71</v>
+        <v>14</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>1.9</v>
+        <v>12.1</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>11.8</v>
+        <v>71</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>16.4</v>
+        <v>6.9</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3777,41 +3773,39 @@
         <v>2942.1</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>18.8</v>
+        <v>49.2</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>12.8</v>
+        <v>13.8</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>19.1</v>
+        <v>4.9</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="I40" s="8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J40" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="inlineStr"/>
+      <c r="L40" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="M40" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="P40" s="3" t="n">
         <v>2.2</v>
-      </c>
-      <c r="K40" s="3" t="inlineStr"/>
-      <c r="L40" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="O40" s="3" t="n">
-        <v>299.5</v>
-      </c>
-      <c r="P40" s="3" t="n">
-        <v>25.5</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>23.8</v>
@@ -3823,7 +3817,7 @@
         <v>17.2</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>68.5</v>
+        <v>58.8</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>12</v>
@@ -3832,7 +3826,7 @@
         <v>19.4</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>16</v>
+        <v>12.1</v>
       </c>
       <c r="X40" s="3" t="n">
         <v>16.8</v>
@@ -3862,20 +3856,20 @@
       <c r="D41" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="E41" s="8" t="n">
+      <c r="E41" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="G41" s="8" t="n">
-        <v>11.1</v>
+      <c r="G41" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>11.1</v>
+        <v>81</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>4.7</v>
@@ -3887,35 +3881,35 @@
         <v>14.8</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>13.6</v>
+        <v>1.3</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" s="8" t="n">
-        <v>123.9</v>
+      <c r="Q41" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>14.5</v>
+        <v>1.5</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>162.5</v>
+        <v>62.5</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="W41" s="8" t="n">
-        <v>72</v>
+        <v>19</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>18.2</v>
@@ -3924,7 +3918,7 @@
         <v>83</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3940,22 +3934,24 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>349.1</v>
-      </c>
-      <c r="D42" s="8" t="n">
+        <v>340.1</v>
+      </c>
+      <c r="D42" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>12.8</v>
+        <v>14.7</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="8" t="n">
+      <c r="H42" s="3" t="n">
         <v>13.7</v>
       </c>
-      <c r="I42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="J42" s="3" t="n">
         <v>4</v>
       </c>
@@ -3963,10 +3959,10 @@
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>11.4</v>
+        <v>14.6</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>14.6</v>
@@ -3978,16 +3974,16 @@
         <v>2</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>43.4</v>
+        <v>18</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>16</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>1460.5</v>
+        <v>60.5</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>10.4</v>
@@ -4019,41 +4015,41 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>517</v>
+        <v>537</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>0.1</v>
+        <v>49.5</v>
       </c>
       <c r="E43" s="3" t="inlineStr"/>
       <c r="F43" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="G43" s="8" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>11.4</v>
+      <c r="G43" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>11.7</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>19.7</v>
+        <v>1.4</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>21.1</v>
+        <v>8</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>4.4</v>
+        <v>15.1</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>16.9</v>
+        <v>1.6</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>2</v>
@@ -4061,23 +4057,23 @@
       <c r="Q43" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="R43" s="8" t="n">
-        <v>16.5</v>
+      <c r="R43" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="S43" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>0.2</v>
+        <v>11.2</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>16.2</v>
@@ -4102,7 +4098,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>653.1</v>
+        <v>223.1</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>23.4</v>
@@ -4127,7 +4123,7 @@
         <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>13.6</v>
+        <v>15.1</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>12.6</v>
@@ -4137,13 +4133,13 @@
         <v>91</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="R44" s="8" t="n">
-        <v>68.09999999999999</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="S44" s="3" t="n">
         <v>13.9</v>
@@ -4152,7 +4148,7 @@
         <v>59.5</v>
       </c>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="n">
+      <c r="V44" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="W44" s="3" t="inlineStr"/>
@@ -4173,76 +4169,76 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>198.5</v>
+        <v>1981.8</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>219.1</v>
+        <v>29.7</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>110.2</v>
+        <v>110.8</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>128.8</v>
+        <v>20.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>13.2</v>
+        <v>15.2</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>26.2</v>
+        <v>286.2</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>10.1</v>
+        <v>180.1</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>82.5</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>91.8</v>
+        <v>31.3</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>290.9</v>
+        <v>240.9</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>112.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>121.6</v>
+        <v>21</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>104.1</v>
+        <v>10.4</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>99.8</v>
+        <v>92.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>381</v>
+        <v>331</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>111.8</v>
+        <v>119.8</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>220.8</v>
+        <v>22</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>36</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>4648.4</v>
+        <v>966.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>28.1</v>
+        <v>28.7</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4258,13 +4254,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>13.3</v>
+        <v>12.3</v>
       </c>
       <c r="F46" s="3" t="n">
         <v>18.4</v>
@@ -4281,23 +4277,21 @@
       <c r="J46" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>4.6</v>
-      </c>
+      <c r="K46" s="3" t="inlineStr"/>
       <c r="L46" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="M46" s="8" t="n">
+      <c r="M46" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="N46" s="8" t="n">
-        <v>38.9</v>
+      <c r="N46" s="3" t="n">
+        <v>6.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>254.1</v>
+        <v>20.4</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>22.8</v>
@@ -4311,20 +4305,18 @@
       <c r="T46" s="3" t="n">
         <v>58.5</v>
       </c>
-      <c r="U46" s="8" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="U46" s="3" t="inlineStr"/>
       <c r="V46" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="W46" s="8" t="n">
+      <c r="W46" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="X46" s="8" t="n">
+      <c r="X46" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>87.8</v>
+        <v>77.8</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>4.8</v>

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_decimal_place_correction.xlsx
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>582.2</v>
+        <v>58.5</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>8.4</v>
+        <v>25.1</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>13.6</v>
@@ -757,19 +757,19 @@
         <v>2.8</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>11.7</v>
+        <v>14.7</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>1.4</v>
+      <c r="N4" s="8" t="n">
+        <v>29.5</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>87</v>
@@ -787,15 +787,15 @@
         <v>16.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="3" t="n">
-        <v>107.1</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>1.6</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="W4" s="3" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr"/>
@@ -813,10 +813,10 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>388.5</v>
+        <v>38.8</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>29.1</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>14.2</v>
@@ -827,47 +827,47 @@
       <c r="G5" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>12.1</v>
+      <c r="H5" s="8" t="n">
+        <v>12.8</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>53.5</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>18.9</v>
+        <v>12.1</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>92</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>18.9</v>
+        <v>16.8</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="S5" s="8" t="n">
-        <v>16.7</v>
+        <v>17.9</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>52</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>15.2</v>
+        <v>1.5</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>20.7</v>
@@ -879,7 +879,7 @@
         <v>18.4</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>7.5</v>
+        <v>75.5</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>6</v>
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>508.9</v>
+        <v>50.8</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>11.8</v>
+        <v>18.5</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>12.8</v>
+        <v>13.9</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>2.4</v>
@@ -922,19 +922,19 @@
         <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="M6" s="8" t="n">
-        <v>30.9</v>
+      <c r="M6" s="3" t="n">
+        <v>13.1</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>19.5</v>
+        <v>45.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>92</v>
+        <v>1.1</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>1.2</v>
@@ -949,7 +949,7 @@
         <v>1.7</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>61.9</v>
+        <v>61.5</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>10.4</v>
@@ -961,13 +961,13 @@
         <v>16.8</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -988,24 +988,26 @@
       <c r="D7" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="n">
+        <v>13.2</v>
+      </c>
       <c r="F7" s="3" t="n">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>10.7</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>11.4</v>
+        <v>2.4</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>14.3</v>
@@ -1013,21 +1015,23 @@
       <c r="M7" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="N7" s="8" t="n">
-        <v>52.1</v>
+      <c r="N7" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>293</v>
+        <v>52.4</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Q7" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>22.5</v>
+      </c>
       <c r="R7" s="3" t="n">
-        <v>17.6</v>
+        <v>1.7</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>17.9</v>
+        <v>12.4</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>59.1</v>
@@ -1036,19 +1040,19 @@
         <v>11.8</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="W7" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W7" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="X7" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>82.2</v>
+        <v>82.5</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>21</v>
+        <v>0.4</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1067,7 +1071,7 @@
         <v>229.8</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>21.9</v>
+        <v>21.5</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>13.8</v>
@@ -1082,25 +1086,25 @@
         <v>12.9</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>6.4</v>
+        <v>11.9</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>16.2</v>
+        <v>40.3</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>93</v>
+        <v>11.6</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.8</v>
@@ -1112,23 +1116,29 @@
         <v>17.5</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>18.1</v>
+        <v>1.8</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="W8" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="W8" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="X8" s="3" t="inlineStr"/>
-      <c r="Y8" s="3" t="inlineStr"/>
-      <c r="Z8" s="3" t="inlineStr"/>
+      <c r="Y8" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1143,26 +1153,28 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2224.9</v>
+        <v>222.4</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>118.5</v>
+        <v>1118.5</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>93.09999999999999</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>20.9</v>
+        <v>30.9</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>63.1</v>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="n">
+        <v>706.4</v>
+      </c>
       <c r="J9" s="3" t="n">
-        <v>260.5</v>
+        <v>260.4</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>51.1</v>
@@ -1171,13 +1183,13 @@
         <v>73.40000000000001</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>16.6</v>
+        <v>166.4</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1590.1</v>
+        <v>59</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>6.6</v>
@@ -1189,29 +1201,27 @@
         <v>88.09999999999999</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>86.8</v>
+        <v>86.2</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>212.6</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V9" s="3" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>117.8</v>
+      </c>
+      <c r="Y9" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="W9" s="3" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="X9" s="3" t="n">
-        <v>89.7</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v>848.1</v>
-      </c>
-      <c r="Z9" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="Z9" s="3" t="inlineStr"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1226,7 +1236,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>495</v>
+        <v>44.5</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>23.7</v>
@@ -1234,7 +1244,7 @@
       <c r="E10" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F10" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="G10" s="3" t="n">
@@ -1244,14 +1254,12 @@
         <v>12.6</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.2</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>3.3</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
         <v>14.7</v>
       </c>
@@ -1262,27 +1270,27 @@
         <v>15.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>921.8</v>
+        <v>99.8</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>113.8</v>
+        <v>1.3</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>9</v>
+        <v>22.8</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="S10" s="8" t="n">
-        <v>78.2</v>
+      <c r="S10" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>62.8</v>
+        <v>19.6</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="W10" s="3" t="n">
@@ -1292,10 +1300,10 @@
         <v>17.9</v>
       </c>
       <c r="Y10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z10" s="3" t="n">
         <v>83</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>3.8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1311,75 +1319,77 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>924.2</v>
+        <v>191.8</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>13.7</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>28.8</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>12.6</v>
+        <v>14.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>1.2</v>
+        <v>12.9</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>14.8</v>
+        <v>14</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>18.1</v>
+        <v>11.9</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>885</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>2.2</v>
+        <v>6.4</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>20.8</v>
+        <v>1.1</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>82</v>
+        <v>140649.1</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>10.6</v>
+        <v>55.1</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>17.9</v>
+        <v>34.1</v>
+      </c>
+      <c r="W11" s="8" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="X11" s="8" t="n">
+        <v>717.5</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="Z11" s="3" t="inlineStr"/>
+        <v>80494</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>3.8</v>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1394,19 +1404,19 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>229</v>
+        <v>229.5</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>99.09999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>13</v>
@@ -1420,17 +1430,17 @@
       <c r="K12" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="L12" s="3" t="n">
-        <v>14.5</v>
+      <c r="L12" s="8" t="n">
+        <v>14.3</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>38.5</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>12.8</v>
+        <v>931.8</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.2</v>
@@ -1441,29 +1451,25 @@
       <c r="R12" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="S12" s="3" t="n">
+      <c r="S12" s="8" t="n">
         <v>17.7</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>6.2</v>
-      </c>
+        <v>24.8</v>
+      </c>
+      <c r="U12" s="3" t="inlineStr"/>
       <c r="V12" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W12" s="3" t="n">
-        <v>14.8</v>
-      </c>
+        <v>4.4</v>
+      </c>
+      <c r="W12" s="3" t="inlineStr"/>
       <c r="X12" s="3" t="n">
-        <v>17.5</v>
+        <v>12.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>18.4</v>
+        <v>940.5</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1494,7 +1500,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>13.1</v>
+        <v>1.3</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.4</v>
@@ -1506,19 +1512,19 @@
         <v>15.7</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>16.9</v>
+        <v>16.1</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>94.5</v>
+        <v>92.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>1.2</v>
+        <v>11</v>
       </c>
       <c r="Q13" s="8" t="n">
         <v>15.8</v>
@@ -1530,22 +1536,22 @@
         <v>16.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>20.5</v>
+        <v>20.9</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>16.7</v>
+        <v>16.9</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>15.8</v>
+        <v>14.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>1.5</v>
+        <v>15.9</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>2.8</v>
@@ -1567,28 +1573,28 @@
         <v>324</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E14" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E14" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>11.4</v>
+        <v>17.6</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>86.8</v>
+        <v>56.8</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>14.4</v>
@@ -1597,40 +1603,40 @@
         <v>13.7</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>15.4</v>
+        <v>15.8</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>94</v>
+        <v>0.1</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>2.8</v>
+        <v>21.7</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="S14" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="U14" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="T14" s="3" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>7.2</v>
-      </c>
       <c r="V14" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X14" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="W14" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X14" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>87.5</v>
+        <v>92</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>1.6</v>
@@ -1651,30 +1657,32 @@
       <c r="C15" s="3" t="n">
         <v>307.9</v>
       </c>
-      <c r="D15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="n">
+        <v>24.8</v>
+      </c>
       <c r="E15" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>7.5</v>
+        <v>18.9</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>12.6</v>
+        <v>13.6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1.2</v>
+        <v>12.4</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>13.8</v>
@@ -1683,10 +1691,10 @@
         <v>15.5</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>96.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>19.8</v>
@@ -1701,22 +1709,22 @@
         <v>73</v>
       </c>
       <c r="U15" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="X15" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="Y15" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W15" s="3" t="n">
+      <c r="Z15" s="3" t="n">
         <v>15.7</v>
-      </c>
-      <c r="X15" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Y15" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="Z15" s="3" t="n">
-        <v>1.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1732,76 +1740,76 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1973.2</v>
+        <v>147.5</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>114.8</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>27.4</v>
+        <v>674.7</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>96</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>17.4</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>164.4</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>6.9</v>
+        <v>16.9</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>46</v>
+        <v>46.8</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>73.2</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>634.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>15.4</v>
+        <v>1140.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>6.9</v>
+        <v>96.5</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>61.4</v>
+        <v>83</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>88</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>3945.2</v>
+        <v>394.5</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>24.8</v>
+        <v>24.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>84</v>
+        <v>84.3</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>18.6</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>85.09999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>428.8</v>
+        <v>1208.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>2.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1817,19 +1825,19 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1469.4</v>
+        <v>295</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>23.9</v>
+        <v>18</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>13.8</v>
+        <v>11.5</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.9</v>
+        <v>9.5</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.9</v>
@@ -1838,28 +1846,28 @@
         <v>1.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>46</v>
+        <v>281.4</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>69.5</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>13.9</v>
+        <v>19.1</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>15.8</v>
+        <v>18.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>11.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>1.2</v>
+        <v>11.2</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>16.7</v>
@@ -1868,25 +1876,25 @@
         <v>17.6</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="V17" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="W17" s="3" t="n">
         <v>16.9</v>
-      </c>
-      <c r="W17" s="3" t="n">
-        <v>15.7</v>
       </c>
       <c r="X17" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>21.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>2</v>
+        <v>15.3</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1902,51 +1910,49 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>428.8</v>
+        <v>428.3</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>18.1</v>
+        <v>18.7</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H18" s="3" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="H18" s="8" t="n">
         <v>10.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.6</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" s="8" t="n">
         <v>13</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>19.4</v>
+        <v>14.4</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="P18" s="3" t="n">
-        <v>1.4</v>
-      </c>
+      <c r="P18" s="3" t="inlineStr"/>
       <c r="Q18" s="3" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="R18" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R18" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -1956,22 +1962,22 @@
         <v>69.09999999999999</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="W18" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="W18" s="8" t="n">
         <v>16</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>17</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>81.8</v>
+        <v>84</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1990,7 +1996,7 @@
         <v>440.6</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>14</v>
@@ -1998,14 +2004,14 @@
       <c r="F19" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>13</v>
+      <c r="G19" s="8" t="n">
+        <v>14</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>3.4</v>
@@ -2013,23 +2019,23 @@
       <c r="K19" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="8" t="n">
         <v>15.1</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>1.4</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>46.4</v>
+        <v>15.5</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Q19" s="3" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
+      </c>
+      <c r="Q19" s="8" t="n">
+        <v>14.9</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>18.1</v>
@@ -2044,19 +2050,19 @@
         <v>14.4</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="W19" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="X19" s="8" t="n">
-        <v>185.3</v>
+        <v>19.8</v>
+      </c>
+      <c r="W19" s="8" t="n">
+        <v>87</v>
+      </c>
+      <c r="X19" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>81</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>127.4</v>
+        <v>17.4</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2075,49 +2081,49 @@
         <v>153.1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E20" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="E20" s="8" t="n">
         <v>13.8</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.7</v>
+        <v>17.3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>13</v>
+        <v>11.8</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>3.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="L20" s="8" t="n">
-        <v>19.4</v>
+      <c r="L20" s="3" t="n">
+        <v>15.4</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>15.1</v>
+        <v>45.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.5</v>
+        <v>9</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>2</v>
+        <v>20.5</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>87.59999999999999</v>
+        <v>17.6</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>18.5</v>
@@ -2126,13 +2132,13 @@
         <v>76.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="V20" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="V20" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>75.5</v>
+        <v>16.8</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>18.6</v>
@@ -2160,7 +2166,7 @@
         <v>261.7</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>20.6</v>
+        <v>21.9</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>14.7</v>
@@ -2169,10 +2175,10 @@
         <v>18.3</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>19.9</v>
+        <v>14.1</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>11.1</v>
@@ -2183,29 +2189,29 @@
       <c r="K21" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="L21" s="8" t="n">
-        <v>56.2</v>
+      <c r="L21" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>121.3</v>
+        <v>11.7</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>90.8</v>
+        <v>99.8</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q21" s="3" t="n">
-        <v>21.4</v>
+      <c r="Q21" s="8" t="n">
+        <v>21.5</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>43.1</v>
+        <v>18.9</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>74</v>
@@ -2213,17 +2219,17 @@
       <c r="U21" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V21" s="8" t="n">
-        <v>18.2</v>
+      <c r="V21" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>17</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>880.9</v>
+        <v>87</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>2.8</v>
@@ -2248,37 +2254,37 @@
         <v>20.6</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>18.8</v>
+        <v>14.4</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="H22" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H22" s="8" t="n">
         <v>13.4</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>12.5</v>
+        <v>15.6</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N22" s="8" t="n">
-        <v>68.90000000000001</v>
+        <v>1.4</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>1</v>
+        <v>91.8</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>1.8</v>
@@ -2289,17 +2295,17 @@
       <c r="R22" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="S22" s="8" t="n">
+      <c r="S22" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>740.8</v>
+        <v>74</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>6.2</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>16.9</v>
@@ -2308,10 +2314,10 @@
         <v>18.9</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>94.5</v>
+        <v>947</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>1</v>
+        <v>10.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2327,46 +2333,44 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>477.4</v>
+        <v>177.2</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>113.1</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>29.4</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>91</v>
+        <v>91.8</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2654</v>
+        <v>94.3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>636.4</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>80.8</v>
-      </c>
+        <v>61.2</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="n">
         <v>9.9</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>38.2</v>
+        <v>0.3</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>161.4</v>
+        <v>16.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>14.6</v>
+        <v>12.2</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>31.6</v>
+        <v>30.4</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>109</v>
@@ -2384,16 +2388,16 @@
         <v>40.6</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>919.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>942.1</v>
+        <v>9</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>148.8</v>
+        <v>929.5</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>13.8</v>
@@ -2420,14 +2424,14 @@
       <c r="E24" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F24" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>636.4</v>
+        <v>12.9</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>1.5</v>
@@ -2436,19 +2440,19 @@
         <v>1.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>38.2</v>
+        <v>0.5</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>14.4</v>
+        <v>15.2</v>
+      </c>
+      <c r="M24" s="8" t="n">
+        <v>43.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>221.1</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>1.4</v>
@@ -2457,7 +2461,7 @@
         <v>21.8</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>47.8</v>
+        <v>17.8</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>18.1</v>
@@ -2468,14 +2472,14 @@
       <c r="U24" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="W24" s="8" t="n">
+      <c r="W24" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>87.09999999999999</v>
@@ -2497,61 +2501,59 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>130.4</v>
+        <v>28</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="E25" s="8" t="n">
-        <v>643.1</v>
-      </c>
-      <c r="F25" s="3" t="n">
+      <c r="E25" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F25" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>12.9</v>
+        <v>1.1</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>2</v>
+        <v>10.1</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>5.9</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>15.1</v>
+        <v>13.1</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>34.2</v>
+        <v>84.2</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>910.8</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>11.4</v>
-      </c>
+        <v>91.5</v>
+      </c>
+      <c r="P25" s="3" t="inlineStr"/>
       <c r="Q25" s="3" t="n">
-        <v>21.9</v>
+        <v>28.5</v>
       </c>
       <c r="R25" s="8" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="S25" s="8" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>49.5</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>16.6</v>
@@ -2560,13 +2562,13 @@
         <v>15.9</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>18.1</v>
+        <v>1.4</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>94</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2582,16 +2584,16 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>87.8</v>
+        <v>32.6</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>23.5</v>
+        <v>22.5</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>14.4</v>
+        <v>13.6</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>18.9</v>
+        <v>1.8</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>8.9</v>
@@ -2600,19 +2602,19 @@
         <v>12.9</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>14.6</v>
+        <v>3.9</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>84.59999999999999</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>14.9</v>
+        <v>1.4</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>11.5</v>
@@ -2621,13 +2623,13 @@
         <v>95</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>11.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="R26" s="3" t="n">
-        <v>17.3</v>
+      <c r="R26" s="8" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>17.8</v>
@@ -2644,14 +2646,14 @@
       <c r="W26" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="X26" s="3" t="n">
+      <c r="X26" s="8" t="n">
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>2.5</v>
+        <v>88.5</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>1.6</v>
+        <v>12.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2667,49 +2669,47 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>5.9</v>
+        <v>12.8</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>13.8</v>
+        <v>23.5</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>14.4</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>14.1</v>
+        <v>1.8</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>9.1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>4.4</v>
-      </c>
+        <v>1.4</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="L27" s="8" t="n">
         <v>15.4</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.6</v>
+        <v>18.8</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>94</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>20.8</v>
+        <v>1.2</v>
+      </c>
+      <c r="Q27" s="8" t="n">
+        <v>10.8</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>17.9</v>
@@ -2718,16 +2718,16 @@
         <v>19</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>71</v>
+        <v>717</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>5.6</v>
+        <v>2.6</v>
       </c>
       <c r="V27" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>15.8</v>
+        <v>16.8</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>18.5</v>
@@ -2752,40 +2752,40 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>305.9</v>
+        <v>30.5</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>11.9</v>
+        <v>17.9</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>8</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>19.4</v>
+        <v>1.5</v>
+      </c>
+      <c r="K28" s="8" t="n">
+        <v>15.4</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="M28" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M28" s="8" t="n">
         <v>14.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.4</v>
+        <v>18.5</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>95</v>
@@ -2794,13 +2794,13 @@
         <v>0.8</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>20.5</v>
+        <v>20.9</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>17</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>17.2</v>
+        <v>41.5</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>72.8</v>
@@ -2821,7 +2821,7 @@
         <v>83.8</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>3.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2846,37 +2846,37 @@
         <v>13.8</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>17.1</v>
+        <v>17.5</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>84.5</v>
+        <v>8.1</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>23.8</v>
+        <v>13.8</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>6.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L29" s="8" t="n">
         <v>14.9</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>14.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.6</v>
+        <v>11.1</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>95</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>21.7</v>
@@ -2888,7 +2888,7 @@
         <v>18.2</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>10</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>7.8</v>
@@ -2899,8 +2899,8 @@
       <c r="W29" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="X29" s="3" t="n">
-        <v>18.2</v>
+      <c r="X29" s="8" t="n">
+        <v>82.09999999999999</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>85</v>
@@ -2922,73 +2922,69 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1689.9</v>
+        <v>1609.9</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>1129.8</v>
       </c>
-      <c r="E30" s="3" t="n">
-        <v>60.6</v>
-      </c>
+      <c r="E30" s="3" t="inlineStr"/>
       <c r="F30" s="3" t="n">
         <v>90.59999999999999</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>43.7</v>
+        <v>49.7</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>9.1</v>
+        <v>19.1</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>38.6</v>
       </c>
-      <c r="L30" s="3" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="L30" s="3" t="inlineStr"/>
       <c r="M30" s="3" t="n">
         <v>11.7</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>1.6</v>
+        <v>7.9</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>479.8</v>
+        <v>0.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>105.2</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>27.4</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>90.09999999999999</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>561.8</v>
+        <v>561</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>394.6</v>
+        <v>34.5</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>18.8</v>
+        <v>88.8</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>88</v>
+        <v>88.2</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>416.8</v>
+        <v>441</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>12.2</v>
@@ -3010,7 +3006,7 @@
         <v>322</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2.2</v>
+        <v>22.5</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>13.7</v>
@@ -3022,7 +3018,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>28.2</v>
+        <v>18.3</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>1.3</v>
@@ -3030,20 +3026,16 @@
       <c r="J31" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>14.9</v>
-      </c>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr"/>
       <c r="M31" s="3" t="n">
-        <v>1.4</v>
+        <v>14.7</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>16.1</v>
+        <v>0.5</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>16.8</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>1</v>
@@ -3058,25 +3050,25 @@
         <v>18.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>116.3</v>
+        <v>29.3</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>6.2</v>
+        <v>6.9</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>17.6</v>
+        <v>18.6</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>17.7</v>
+        <v>1.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>88.3</v>
+        <v>119.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>4.4</v>
+        <v>214.4</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3092,40 +3084,38 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>481.8</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>24.9</v>
-      </c>
+        <v>23.5</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr"/>
       <c r="E32" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>14.2</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>19.4</v>
+        <v>13.4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>16.1</v>
+        <v>16.8</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>105.1</v>
       </c>
-      <c r="N32" s="3" t="n">
-        <v>16.1</v>
+      <c r="N32" s="8" t="n">
+        <v>12.8</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>83</v>
@@ -3136,14 +3126,14 @@
       <c r="Q32" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="R32" s="8" t="n">
-        <v>15.8</v>
+      <c r="R32" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>18.8</v>
+        <v>18.2</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>2.2</v>
@@ -3155,13 +3145,13 @@
         <v>15.6</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>17.7</v>
+        <v>18.8</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>8</v>
+        <v>0.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3177,46 +3167,46 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>422.8</v>
-      </c>
-      <c r="D33" s="8" t="n">
-        <v>49.1</v>
+        <v>1482.8</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>24.8</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>66184.5</v>
+        <v>12.6</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="G33" s="8" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>20.6</v>
+        <v>19.5</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>82.59999999999999</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>4.9</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>12.9</v>
+        <v>86.5</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>16.1</v>
+        <v>13.7</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>13</v>
       </c>
       <c r="N33" s="8" t="n">
-        <v>92.40000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>93</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>23.8</v>
@@ -3228,19 +3218,19 @@
         <v>12.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>319.5</v>
+        <v>21.2</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V33" s="3" t="n">
+      <c r="V33" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="W33" s="8" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>16.6</v>
+      <c r="W33" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="X33" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="Y33" s="3" t="n">
         <v>71</v>
@@ -3262,28 +3252,28 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>492.8</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>25</v>
+        <v>482.8</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>44.1</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>3.6</v>
+        <v>11.5</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="G34" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="G34" s="8" t="n">
         <v>12.6</v>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>18.3</v>
+      <c r="H34" s="8" t="n">
+        <v>109.5</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0</v>
@@ -3292,10 +3282,10 @@
         <v>12.5</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>91.59999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>11.1</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>92</v>
@@ -3307,7 +3297,7 @@
         <v>23.9</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>1.7</v>
+        <v>17.8</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>16.8</v>
@@ -3322,15 +3312,15 @@
         <v>18</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X34" s="3" t="inlineStr"/>
+        <v>12.8</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Y34" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="Z34" s="3" t="n">
-        <v>4.2</v>
-      </c>
+      <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -3345,25 +3335,25 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="D35" s="8" t="n">
-        <v>18</v>
+        <v>9492.799999999999</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>25</v>
       </c>
       <c r="E35" s="8" t="n">
         <v>13.6</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G35" s="8" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>279.3</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>2.4</v>
+        <v>44.6</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>4</v>
@@ -3375,19 +3365,19 @@
         <v>16.6</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>17.8</v>
+        <v>11.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>90</v>
+        <v>910</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q35" s="3" t="n">
-        <v>24.8</v>
+      <c r="Q35" s="8" t="n">
+        <v>94.5</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>18.8</v>
@@ -3396,22 +3386,22 @@
         <v>18.2</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>60</v>
+        <v>600.8</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X35" s="3" t="n">
-        <v>18.5</v>
+        <v>17.1</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>82.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>75.5</v>
+        <v>125.5</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>6</v>
@@ -3430,25 +3420,25 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>498.3</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E36" s="3" t="n">
+        <v>9498.9</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="E36" s="8" t="n">
         <v>13.9</v>
       </c>
-      <c r="F36" s="8" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>10.3</v>
+      <c r="F36" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>410.3</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.4</v>
+        <v>12.7</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>4</v>
@@ -3456,14 +3446,14 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="3" t="n">
-        <v>16.6</v>
+      <c r="L36" s="8" t="n">
+        <v>86.59999999999999</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="N36" s="8" t="n">
-        <v>81.09999999999999</v>
+        <v>17.4</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>91</v>
@@ -3471,20 +3461,20 @@
       <c r="P36" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q36" s="3" t="n">
-        <v>29.2</v>
+      <c r="Q36" s="8" t="n">
+        <v>88.09999999999999</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>55.1</v>
+        <v>52.1</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>12.8</v>
+        <v>11.2</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>18.4</v>
@@ -3492,14 +3482,14 @@
       <c r="W36" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="X36" s="3" t="n">
-        <v>1.6</v>
+      <c r="X36" s="8" t="n">
+        <v>66.59999999999999</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3515,46 +3505,44 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>128.1</v>
+        <v>2192.8</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>12.1</v>
+        <v>119.1</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>69.8</v>
+        <v>665.7</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>18.8</v>
-      </c>
+        <v>53.3</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr"/>
       <c r="I37" s="3" t="n">
         <v>110.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>12.6</v>
+        <v>17.6</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>121.8</v>
+        <v>12.1</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>15.6</v>
+        <v>711.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>11.1</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>44930.3</v>
+        <v>4420.3</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>113.4</v>
@@ -3563,28 +3551,28 @@
         <v>81</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>24.8</v>
+        <v>84.8</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>313.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>24.8</v>
+        <v>234.8</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>91</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>83.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>41252.4</v>
+        <v>409.8</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>4.5</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3600,43 +3588,41 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>438.6</v>
+        <v>43.8</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>12.2</v>
+        <v>13.9</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>18.5</v>
+        <v>10.8</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>22.3</v>
+        <v>12.3</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>2.1</v>
+        <v>12.1</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K38" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>15.1</v>
+        <v>151.3</v>
       </c>
       <c r="M38" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="N38" s="8" t="n">
-        <v>58.1</v>
+      <c r="N38" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>89.8</v>
+        <v>15.2</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>1.8</v>
@@ -3648,10 +3634,10 @@
         <v>17.4</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>480.5</v>
+        <v>17</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>63.9</v>
+        <v>82.7</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>11</v>
@@ -3660,16 +3646,16 @@
         <v>18.2</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>15.1</v>
+        <v>16.1</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>21.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>4</v>
+        <v>89.8</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3685,76 +3671,72 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>2392.3</v>
+        <v>39595.3</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>23</v>
+        <v>24.2</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="G39" s="8" t="n">
-        <v>11.9</v>
+      <c r="G39" s="3" t="n">
+        <v>11.5</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J39" s="3" t="n">
-        <v>5.2</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="3" t="n">
-        <v>15.9</v>
+        <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N39" s="8" t="n">
-        <v>1.5</v>
+        <v>16.1</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>29.6</v>
+        <v>23.6</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="S39" s="3" t="n">
-        <v>19</v>
+      <c r="S39" s="8" t="n">
+        <v>20.9</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>52</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>1.9</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="V39" s="3" t="inlineStr"/>
       <c r="W39" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="X39" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="X39" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>71</v>
+        <v>1.4</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>6.9</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3770,42 +3752,46 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>2942.1</v>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>49.2</v>
+        <v>545.4</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>29.3</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>13.8</v>
+        <v>12.8</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>4.9</v>
+        <v>19.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr"/>
-      <c r="K40" s="3" t="inlineStr"/>
+        <v>0.3</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="L40" s="3" t="n">
         <v>16</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>23.8</v>
@@ -3814,7 +3800,7 @@
         <v>17.9</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>58.8</v>
@@ -3825,17 +3811,17 @@
       <c r="V40" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="W40" s="3" t="n">
-        <v>12.1</v>
+      <c r="W40" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>16.8</v>
+        <v>1.6</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>6.2</v>
+        <v>408.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3851,28 +3837,28 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>408.4</v>
-      </c>
-      <c r="D41" s="3" t="n">
+        <v>340.1</v>
+      </c>
+      <c r="D41" s="8" t="n">
         <v>23.7</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>13.1</v>
+        <v>18.1</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H41" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H41" s="8" t="n">
         <v>10.8</v>
       </c>
-      <c r="I41" s="8" t="n">
-        <v>81</v>
+      <c r="I41" s="3" t="n">
+        <v>2.4</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
@@ -3881,44 +3867,46 @@
         <v>14.8</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N41" s="3" t="inlineStr"/>
+        <v>15.6</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>19.2</v>
+      </c>
       <c r="O41" s="3" t="n">
-        <v>82</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>1.8</v>
+        <v>23.2</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>17.8</v>
+        <v>18</v>
+      </c>
+      <c r="S41" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62.5</v>
+        <v>62.2</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>1</v>
+        <v>10.6</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>19</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>18.2</v>
+        <v>14.6</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>83</v>
+        <v>113.8</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>19.2</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3934,50 +3922,52 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>340.1</v>
+        <v>331</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>22.4</v>
+        <v>22.9</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>14.7</v>
+        <v>11.4</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G42" s="3" t="inlineStr"/>
+        <v>18.5</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="H42" s="3" t="n">
-        <v>13.7</v>
+        <v>11.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>14.6</v>
+        <v>16.2</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>1.3</v>
+        <v>15.1</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>14.6</v>
+        <v>16.1</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>2</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>4.8</v>
+        <v>16.7</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>16</v>
@@ -3989,17 +3979,19 @@
         <v>10.4</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>18.2</v>
+        <v>20.4</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X42" s="3" t="inlineStr"/>
+        <v>12.1</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="Y42" s="3" t="n">
-        <v>87</v>
+        <v>110.1</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>2.6</v>
+        <v>58</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4015,74 +4007,76 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>537</v>
+        <v>557.1</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="E43" s="3" t="inlineStr"/>
+        <v>13.4</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="F43" s="3" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>11.7</v>
+        <v>10.8</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>99.59999999999999</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>1.4</v>
+        <v>28.8</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>15.1</v>
+        <v>14.2</v>
+      </c>
+      <c r="M43" s="8" t="n">
+        <v>35.4</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>1.6</v>
+        <v>16.5</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>15.6</v>
+        <v>12.6</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>11.2</v>
+        <v>186.7</v>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v>19.4</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>0.1</v>
+        <v>91</v>
+      </c>
+      <c r="W43" s="8" t="n">
+        <v>22.6</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>16.2</v>
+        <v>5</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>81.8</v>
+        <v>1.9</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4098,63 +4092,77 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>223.1</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>12.6</v>
+        <v>2983</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>91.09999999999999</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="G44" s="3" t="inlineStr"/>
+        <v>10.5</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>62</v>
+      </c>
       <c r="H44" s="3" t="n">
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>2.6</v>
+        <v>15.2</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>5</v>
+        <v>26.2</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>15.1</v>
+        <v>1.1</v>
+      </c>
+      <c r="L44" s="8" t="n">
+        <v>83.59999999999999</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="N44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="n">
+        <v>19.1</v>
+      </c>
       <c r="O44" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="P44" s="3" t="n">
-        <v>1.4</v>
+        <v>8.1</v>
+      </c>
+      <c r="P44" s="8" t="n">
+        <v>340.9</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>22.2</v>
+        <v>10.6</v>
       </c>
       <c r="R44" s="8" t="n">
-        <v>67.09999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>13.9</v>
+        <v>97.5</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="U44" s="3" t="inlineStr"/>
+        <v>351</v>
+      </c>
+      <c r="U44" s="3" t="n">
+        <v>69</v>
+      </c>
       <c r="V44" s="8" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="W44" s="3" t="inlineStr"/>
-      <c r="X44" s="3" t="inlineStr"/>
-      <c r="Y44" s="3" t="inlineStr"/>
-      <c r="Z44" s="3" t="inlineStr"/>
+        <v>111.5</v>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="Y44" s="3" t="n">
+        <v>466.8</v>
+      </c>
+      <c r="Z44" s="3" t="n">
+        <v>28.1</v>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4169,76 +4177,76 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2282</v>
+        <v>497</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>1981.8</v>
+        <v>23.6</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>29.7</v>
+        <v>13.3</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>110.8</v>
+        <v>18.4</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>62</v>
+        <v>10.3</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>20.8</v>
+        <v>11.8</v>
       </c>
       <c r="I45" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N45" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="J45" s="3" t="n">
-        <v>286.2</v>
-      </c>
-      <c r="K45" s="3" t="n">
-        <v>180.1</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>31.3</v>
-      </c>
       <c r="O45" s="3" t="n">
-        <v>240.9</v>
+        <v>10.1</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>10.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>21</v>
+        <v>922.8</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>10.4</v>
+        <v>17.1</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>92.2</v>
+        <v>16.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>331</v>
+        <v>58.5</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>162</v>
+        <v>11.5</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>119.8</v>
+        <v>118.6</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>22</v>
+        <v>15.9</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>36</v>
+        <v>16.6</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>966.8</v>
+        <v>82.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>28.7</v>
+        <v>44.8</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4257,69 +4265,73 @@
         <v>497</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>23.6</v>
+        <v>0.1</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>12.3</v>
+        <v>0.1</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>18.4</v>
+        <v>0.1</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>10.3</v>
+        <v>145.9</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>11.8</v>
+        <v>1.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L46" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>6.8</v>
+        <v>12.8</v>
+      </c>
+      <c r="N46" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>20.4</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>22.8</v>
+        <v>2.2</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>17.1</v>
+        <v>1.8</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>16.2</v>
+        <v>1</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="U46" s="3" t="inlineStr"/>
+        <v>11.8</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>1414</v>
+      </c>
       <c r="V46" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v>15.9</v>
+        <v>117.5</v>
+      </c>
+      <c r="W46" s="8" t="n">
+        <v>11151.1</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>16.6</v>
+        <v>0.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>77.8</v>
+        <v>112</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>4.8</v>
+        <v>15.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_decimal_place_correction.xlsx
@@ -768,8 +768,8 @@
       <c r="M4" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>29.5</v>
+      <c r="N4" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>87</v>
@@ -787,13 +787,13 @@
         <v>16.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v>18.7</v>
+        <v>1.5</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="W4" s="3" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
@@ -813,10 +813,10 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>93.90000000000001</v>
+        <v>388.3</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>23.7</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>14.2</v>
@@ -827,62 +827,62 @@
       <c r="G5" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="H5" s="8" t="n">
-        <v>12.8</v>
+      <c r="H5" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="L5" s="8" t="n">
-        <v>53.5</v>
+      <c r="L5" s="3" t="n">
+        <v>13.5</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>12.1</v>
+        <v>18.1</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>16.8</v>
+        <v>1.4</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>17.9</v>
+        <v>17.2</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.6</v>
+        <v>13.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>52</v>
+        <v>61.5</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>20.7</v>
+        <v>13</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>17.6</v>
+        <v>2.4</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>18.4</v>
+        <v>13.9</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>75.5</v>
+        <v>12.8</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>6</v>
+        <v>18.5</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -898,43 +898,43 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>50.8</v>
+        <v>508.9</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="E6" s="8" t="n">
-        <v>12.8</v>
+      <c r="E6" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>18.5</v>
+        <v>13.2</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>13.9</v>
+        <v>12</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>13.1</v>
+        <v>13.6</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>45.1</v>
+        <v>15.9</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>1.1</v>
+        <v>22.5</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>1.2</v>
@@ -949,25 +949,25 @@
         <v>1.7</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>61.5</v>
+        <v>18.5</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>10.4</v>
+        <v>512.9</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>18.6</v>
+        <v>10.7</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>16.8</v>
+        <v>22.5</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>18.1</v>
+        <v>17.6</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>27</v>
+        <v>17.4</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -983,76 +983,76 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>512.9</v>
+        <v>22.9</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>23.9</v>
+        <v>21.5</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>12.5</v>
+        <v>17.7</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>10.7</v>
+        <v>7.7</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>8.4</v>
+        <v>1.8</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>98</v>
+        <v>29.9</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>14.3</v>
+        <v>15.1</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>13.6</v>
+        <v>14.1</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>15.8</v>
+        <v>40.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>52.4</v>
+        <v>22.4</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>1.7</v>
+        <v>17.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>12.4</v>
+        <v>18.3</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>59.1</v>
+        <v>64</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>11.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W7" s="8" t="n">
-        <v>16.6</v>
+        <v>19.2</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>17.7</v>
+        <v>76</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>82.5</v>
+        <v>28</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.4</v>
+        <v>5.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1068,76 +1068,76 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>229.8</v>
+        <v>22.2</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>21.5</v>
+        <v>118.5</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>13.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>17.7</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>7.7</v>
+        <v>50.9</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12.9</v>
+        <v>63.1</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.9</v>
+        <v>706.4</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.8</v>
+        <v>260.4</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>11.9</v>
+        <v>51.1</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>15.1</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>14.1</v>
+        <v>60.2</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>40.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>11.6</v>
+        <v>59</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>20.5</v>
+        <v>114</v>
       </c>
       <c r="R8" s="3" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="S8" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="W8" s="8" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="Y8" s="3" t="n">
-        <v>11.4</v>
+        <v>90</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1153,75 +1153,77 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>222.4</v>
+        <v>445</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1118.5</v>
+        <v>23.7</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>93.09999999999999</v>
+        <v>18.6</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>30.9</v>
+        <v>10.2</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>63.1</v>
+        <v>12.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>706.4</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>260.4</v>
+        <v>3.3</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>51.1</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>73.40000000000001</v>
+        <v>14.7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.2</v>
+        <v>13.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>166.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>59</v>
+        <v>21.8</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>114</v>
+        <v>22.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>17.6</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>86.2</v>
+        <v>17.2</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>212.6</v>
+        <v>21.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>23</v>
+        <v>1.1</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>115.1</v>
+        <v>94</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>16</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>117.8</v>
+        <v>89.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="Z9" s="3" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>19.2</v>
+      </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1236,7 +1238,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>44.5</v>
+        <v>45</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>23.7</v>
@@ -1251,32 +1253,34 @@
         <v>10.2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>12.6</v>
+        <v>1.2</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>97.90000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="J10" s="3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="K10" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M10" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="N10" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="N10" s="3" t="n">
-        <v>15.8</v>
-      </c>
       <c r="O10" s="3" t="n">
-        <v>99.8</v>
+        <v>15.3</v>
       </c>
       <c r="P10" s="3" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="Q10" s="3" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>22.8</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>17.6</v>
@@ -1285,12 +1289,12 @@
         <v>17.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>19.6</v>
+        <v>21.5</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V10" s="8" t="n">
+      <c r="V10" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="W10" s="3" t="n">
@@ -1300,10 +1304,10 @@
         <v>17.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>83</v>
+        <v>3.8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1322,7 +1326,7 @@
         <v>191.8</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>13.7</v>
@@ -1331,7 +1335,7 @@
         <v>18.1</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>28.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>14.8</v>
@@ -1343,53 +1347,43 @@
         <v>0.7</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>12.9</v>
+        <v>1.5</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>14</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>11.9</v>
+        <v>17.2</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>6.4</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>1.1</v>
+        <v>17.5</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>140649.1</v>
+        <v>212.4</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>55.1</v>
       </c>
-      <c r="V11" s="3" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="W11" s="8" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="X11" s="8" t="n">
-        <v>717.5</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>80494</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>3.8</v>
-      </c>
+      <c r="V11" s="3" t="inlineStr"/>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1410,7 +1404,7 @@
         <v>22.4</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>17.9</v>
@@ -1418,7 +1412,7 @@
       <c r="G12" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="3" t="n">
         <v>13</v>
       </c>
       <c r="I12" s="3" t="n">
@@ -1430,32 +1424,32 @@
       <c r="K12" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="L12" s="8" t="n">
+      <c r="L12" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="M12" s="8" t="n">
-        <v>83.90000000000001</v>
+      <c r="M12" s="3" t="n">
+        <v>13.5</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>15</v>
+        <v>15.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>931.8</v>
+        <v>98</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="S12" s="8" t="n">
+      <c r="S12" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>24.8</v>
+        <v>74.5</v>
       </c>
       <c r="U12" s="3" t="inlineStr"/>
       <c r="V12" s="3" t="n">
@@ -1463,7 +1457,7 @@
       </c>
       <c r="W12" s="3" t="inlineStr"/>
       <c r="X12" s="3" t="n">
-        <v>12.3</v>
+        <v>18.5</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>940.5</v>
@@ -1500,7 +1494,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>1.3</v>
+        <v>13.5</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.4</v>
@@ -1521,28 +1515,28 @@
         <v>16.1</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>92.5</v>
+        <v>94.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>20.9</v>
+        <v>74.5</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>16.9</v>
+        <v>16.5</v>
       </c>
       <c r="W13" s="3" t="n">
         <v>14.8</v>
@@ -1570,7 +1564,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>324</v>
+        <v>32.4</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>21.8</v>
@@ -1588,13 +1582,13 @@
         <v>12.5</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>56.8</v>
+        <v>26.8</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>14.4</v>
@@ -1603,16 +1597,16 @@
         <v>13.7</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>15.8</v>
+        <v>15.4</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.1</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>21.7</v>
+        <v>21.3</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>17.6</v>
@@ -1621,25 +1615,25 @@
         <v>18.1</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="W14" s="8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="W14" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="X14" s="8" t="n">
+      <c r="X14" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>92</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>1.6</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1658,7 +1652,7 @@
         <v>307.9</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>24.8</v>
+        <v>24.5</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>13.2</v>
@@ -1670,19 +1664,19 @@
         <v>11.3</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>13.6</v>
+        <v>12.6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>12.4</v>
+        <v>1.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>13.8</v>
@@ -1691,7 +1685,7 @@
         <v>15.5</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>25</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.6</v>
@@ -1709,7 +1703,7 @@
         <v>73</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>18.2</v>
@@ -1743,28 +1737,28 @@
         <v>147.5</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>114.8</v>
+        <v>14.8</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>674.7</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>47.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>164.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>5.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>46.8</v>
+        <v>46.5</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>73.2</v>
@@ -1773,10 +1767,10 @@
         <v>634.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1140.4</v>
+        <v>12.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6</v>
@@ -1785,7 +1779,7 @@
         <v>96.5</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>83</v>
+        <v>83.5</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>88.09999999999999</v>
@@ -1794,7 +1788,7 @@
         <v>394.5</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>24.2</v>
+        <v>24.8</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>84.3</v>
@@ -1803,10 +1797,10 @@
         <v>78.59999999999999</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1208.8</v>
+        <v>158.8</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1825,16 +1819,16 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>295</v>
+        <v>29.5</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>9.5</v>
@@ -1846,25 +1840,25 @@
         <v>1.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>281.4</v>
-      </c>
-      <c r="K17" s="8" t="n">
-        <v>69.5</v>
+        <v>121.4</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>19.1</v>
+        <v>13.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>18.1</v>
+        <v>15.2</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>11.8</v>
+        <v>15.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>19.3</v>
@@ -1879,7 +1873,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>18.9</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>5</v>
@@ -1891,7 +1885,7 @@
         <v>17.2</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>21.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>15.3</v>
@@ -1910,13 +1904,13 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>428.3</v>
+        <v>428.5</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>18.7</v>
@@ -1924,11 +1918,11 @@
       <c r="G18" s="3" t="n">
         <v>48.4</v>
       </c>
-      <c r="H18" s="8" t="n">
+      <c r="H18" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.6</v>
@@ -1939,7 +1933,7 @@
       <c r="L18" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="M18" s="8" t="n">
+      <c r="M18" s="3" t="n">
         <v>13</v>
       </c>
       <c r="N18" s="3" t="n">
@@ -1952,7 +1946,7 @@
       <c r="Q18" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="R18" s="8" t="n">
+      <c r="R18" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -1962,16 +1956,16 @@
         <v>69.09999999999999</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="W18" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="X18" s="8" t="n">
-        <v>70.09999999999999</v>
+      <c r="X18" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>84</v>
@@ -1993,7 +1987,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>440.6</v>
+        <v>40.6</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>25</v>
@@ -2004,7 +1998,7 @@
       <c r="F19" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="G19" s="8" t="n">
+      <c r="G19" s="3" t="n">
         <v>14</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2019,23 +2013,23 @@
       <c r="K19" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="L19" s="8" t="n">
+      <c r="L19" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>1.4</v>
+        <v>14.3</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q19" s="8" t="n">
-        <v>14.9</v>
+        <v>1.4</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>18.1</v>
@@ -2050,10 +2044,10 @@
         <v>14.4</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="W19" s="8" t="n">
-        <v>87</v>
+        <v>19.5</v>
+      </c>
+      <c r="W19" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>18.3</v>
@@ -2062,7 +2056,7 @@
         <v>81</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>17.4</v>
+        <v>4.4</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2083,23 +2077,23 @@
       <c r="D20" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="E20" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>11.8</v>
+        <v>8.9</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>23.8</v>
+        <v>13.8</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>5.6</v>
@@ -2111,13 +2105,13 @@
         <v>45.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.4</v>
+        <v>17.8</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>9</v>
+        <v>0.5</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>20.5</v>
@@ -2134,7 +2128,7 @@
       <c r="U20" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="V20" s="8" t="n">
+      <c r="V20" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="W20" s="3" t="n">
@@ -2163,7 +2157,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>261.7</v>
+        <v>251.7</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>21.9</v>
@@ -2175,16 +2169,16 @@
         <v>18.3</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>14.1</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>10.9</v>
@@ -2196,16 +2190,16 @@
         <v>15.2</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>11.7</v>
+        <v>1.6</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>99.8</v>
+        <v>90.8</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q21" s="8" t="n">
-        <v>21.5</v>
+      <c r="Q21" s="3" t="n">
+        <v>21.4</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>18.1</v>
@@ -2248,7 +2242,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>123.3</v>
+        <v>193.3</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>20.6</v>
@@ -2260,31 +2254,31 @@
         <v>17.5</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="H22" s="8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H22" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>1.4</v>
+        <v>14.6</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>91.8</v>
+        <v>91</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>1.8</v>
@@ -2317,7 +2311,7 @@
         <v>947</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>10.9</v>
+        <v>1</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2339,29 +2333,29 @@
         <v>113.1</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>29.4</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>91.8</v>
+        <v>92.5</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>94.3</v>
+        <v>43.7</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>61.2</v>
       </c>
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>16.2</v>
+        <v>76.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>12.2</v>
+        <v>72.2</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>30.4</v>
@@ -2379,7 +2373,7 @@
         <v>88.8</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>90.2</v>
+        <v>90.5</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>347.9</v>
@@ -2388,7 +2382,7 @@
         <v>40.6</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="W23" s="3" t="n">
         <v>81.09999999999999</v>
@@ -2397,7 +2391,7 @@
         <v>9</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>929.5</v>
+        <v>35.5</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>13.8</v>
@@ -2416,7 +2410,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>215.4</v>
+        <v>29.5</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>22.6</v>
@@ -2431,7 +2425,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>12.9</v>
+        <v>22.9</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>1.5</v>
@@ -2440,19 +2434,19 @@
         <v>1.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="M24" s="8" t="n">
-        <v>43.4</v>
+      <c r="M24" s="3" t="n">
+        <v>14.4</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>1.4</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>221.1</v>
+        <v>22.1</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>1.4</v>
@@ -2472,7 +2466,7 @@
       <c r="U24" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="V24" s="8" t="n">
+      <c r="V24" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="W24" s="3" t="n">
@@ -2501,16 +2495,16 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>28</v>
+        <v>400.4</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F25" s="8" t="n">
-        <v>18.8</v>
+        <v>13</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>9</v>
@@ -2528,10 +2522,10 @@
         <v>5.9</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>84.2</v>
+        <v>15.1</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>14.2</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>1.5</v>
@@ -2541,13 +2535,13 @@
       </c>
       <c r="P25" s="3" t="inlineStr"/>
       <c r="Q25" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="R25" s="8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="R25" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>11.6</v>
+        <v>17.6</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>49.5</v>
@@ -2584,7 +2578,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>32.6</v>
+        <v>326</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>22.5</v>
@@ -2599,7 +2593,7 @@
         <v>8.9</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.4</v>
@@ -2610,14 +2604,14 @@
       <c r="K26" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="L26" s="8" t="n">
-        <v>84.59999999999999</v>
+      <c r="L26" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>1.4</v>
+        <v>14.1</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>95</v>
@@ -2628,8 +2622,8 @@
       <c r="Q26" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="R26" s="8" t="n">
-        <v>8.800000000000001</v>
+      <c r="R26" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>17.8</v>
@@ -2646,14 +2640,14 @@
       <c r="W26" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="X26" s="8" t="n">
+      <c r="X26" s="3" t="n">
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>88.5</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2669,12 +2663,12 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>12.8</v>
+        <v>288.8</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="E27" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="F27" s="3" t="n">
@@ -2684,7 +2678,7 @@
         <v>9.1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.4</v>
+        <v>14.9</v>
       </c>
       <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="n">
@@ -2693,14 +2687,14 @@
       <c r="K27" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="L27" s="8" t="n">
+      <c r="L27" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>18.8</v>
+        <v>16.8</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>94</v>
@@ -2708,8 +2702,8 @@
       <c r="P27" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q27" s="8" t="n">
-        <v>10.8</v>
+      <c r="Q27" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>17.9</v>
@@ -2718,10 +2712,10 @@
         <v>19</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>717</v>
+        <v>77</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
       <c r="V27" s="3" t="n">
         <v>17.8</v>
@@ -2752,7 +2746,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>30.5</v>
+        <v>305.9</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>21.8</v>
@@ -2767,7 +2761,7 @@
         <v>8</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>82.8</v>
+        <v>23.8</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.9</v>
@@ -2775,17 +2769,17 @@
       <c r="J28" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="K28" s="8" t="n">
+      <c r="K28" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="M28" s="8" t="n">
+      <c r="M28" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>18.5</v>
+        <v>1.8</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>95</v>
@@ -2794,7 +2788,7 @@
         <v>0.8</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>20.9</v>
+        <v>20.5</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>17</v>
@@ -2818,10 +2812,10 @@
         <v>15.8</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>83.8</v>
+        <v>83</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2846,7 +2840,7 @@
         <v>13.8</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>17.5</v>
+        <v>1.7</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>8.1</v>
@@ -2855,22 +2849,22 @@
         <v>13.8</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="L29" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L29" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>11.1</v>
+        <v>14.1</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>95</v>
@@ -2879,7 +2873,7 @@
         <v>0.8</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>17.8</v>
@@ -2888,7 +2882,7 @@
         <v>18.2</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>7.8</v>
@@ -2899,8 +2893,8 @@
       <c r="W29" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="X29" s="8" t="n">
-        <v>82.09999999999999</v>
+      <c r="X29" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>85</v>
@@ -2925,7 +2919,7 @@
         <v>1609.9</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1129.8</v>
+        <v>112.9</v>
       </c>
       <c r="E30" s="3" t="inlineStr"/>
       <c r="F30" s="3" t="n">
@@ -2935,23 +2929,23 @@
         <v>49.7</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>38.6</v>
+        <v>35.6</v>
       </c>
       <c r="L30" s="3" t="inlineStr"/>
       <c r="M30" s="3" t="n">
-        <v>11.7</v>
+        <v>71.7</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>7.9</v>
+        <v>79.8</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>0.5</v>
@@ -2969,10 +2963,10 @@
         <v>90.09999999999999</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>561</v>
+        <v>361.9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>34.5</v>
+        <v>34.6</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>88.8</v>
@@ -2981,7 +2975,7 @@
         <v>81.09999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>88.2</v>
+        <v>88.5</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>441</v>
@@ -3029,10 +3023,10 @@
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="inlineStr"/>
       <c r="M31" s="3" t="n">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>16.8</v>
@@ -3050,25 +3044,25 @@
         <v>18.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>29.3</v>
+        <v>79.8</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>6.9</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>18.6</v>
+        <v>17.6</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>1.4</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>119.2</v>
+        <v>19.8</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>214.4</v>
+        <v>24.4</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3084,7 +3078,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>23.5</v>
+        <v>235.5</v>
       </c>
       <c r="D32" s="3" t="inlineStr"/>
       <c r="E32" s="3" t="n">
@@ -3094,7 +3088,7 @@
         <v>17.9</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1.3</v>
+        <v>7.3</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>13.4</v>
@@ -3109,13 +3103,13 @@
         <v>12.7</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>16.8</v>
+        <v>16.3</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>105.1</v>
       </c>
-      <c r="N32" s="8" t="n">
-        <v>12.8</v>
+      <c r="N32" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>83</v>
@@ -3127,10 +3121,10 @@
         <v>17</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>18.8</v>
+        <v>15.8</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>18.2</v>
+        <v>17</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>90</v>
@@ -3145,13 +3139,13 @@
         <v>15.6</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>18.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y32" s="3" t="n">
         <v>97</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3167,22 +3161,22 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1482.8</v>
+        <v>482.8</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>24.8</v>
+        <v>24.2</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="H33" s="8" t="n">
-        <v>82.59999999999999</v>
+      <c r="H33" s="3" t="n">
+        <v>20.6</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>2.6</v>
@@ -3191,7 +3185,7 @@
         <v>4.9</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>86.5</v>
+        <v>1.8</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>13.7</v>
@@ -3199,14 +3193,14 @@
       <c r="M33" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="N33" s="8" t="n">
-        <v>84.8</v>
+      <c r="N33" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>93</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>23.8</v>
@@ -3215,25 +3209,25 @@
         <v>16.8</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>12.2</v>
+        <v>15.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>21.2</v>
+        <v>51.5</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V33" s="8" t="n">
+      <c r="V33" s="3" t="n">
         <v>18</v>
       </c>
       <c r="W33" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="X33" s="8" t="n">
+      <c r="X33" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Z33" s="3" t="n">
         <v>4.8</v>
@@ -3254,8 +3248,8 @@
       <c r="C34" s="3" t="n">
         <v>482.8</v>
       </c>
-      <c r="D34" s="8" t="n">
-        <v>44.1</v>
+      <c r="D34" s="3" t="n">
+        <v>24.1</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>11.5</v>
@@ -3263,14 +3257,14 @@
       <c r="F34" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="G34" s="8" t="n">
+      <c r="G34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="H34" s="8" t="n">
-        <v>109.5</v>
+      <c r="H34" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.9</v>
@@ -3281,11 +3275,11 @@
       <c r="L34" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M34" s="8" t="n">
-        <v>11.6</v>
+      <c r="M34" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>11.1</v>
+        <v>13.1</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>92</v>
@@ -3297,7 +3291,7 @@
         <v>23.9</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>16.8</v>
@@ -3312,13 +3306,13 @@
         <v>18</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>12.8</v>
+        <v>15.8</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
@@ -3335,19 +3329,19 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>9492.799999999999</v>
+        <v>492.8</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="E35" s="8" t="n">
+      <c r="E35" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>1.9</v>
+        <v>19.3</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1.1</v>
+        <v>11.4</v>
       </c>
       <c r="H35" s="8" t="n">
         <v>279.3</v>
@@ -3368,16 +3362,16 @@
         <v>15.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>910</v>
+        <v>10</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q35" s="8" t="n">
-        <v>94.5</v>
+      <c r="Q35" s="3" t="n">
+        <v>24.5</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>18.8</v>
@@ -3386,22 +3380,22 @@
         <v>18.2</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>600.8</v>
+        <v>60</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="X35" s="8" t="n">
-        <v>82.8</v>
+        <v>17.7</v>
+      </c>
+      <c r="X35" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>125.5</v>
+        <v>75.5</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>6</v>
@@ -3420,19 +3414,19 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>9498.9</v>
-      </c>
-      <c r="D36" s="8" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="E36" s="8" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E36" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="G36" s="8" t="n">
-        <v>410.3</v>
+        <v>12.1</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>10.3</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>12.7</v>
@@ -3446,14 +3440,14 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="8" t="n">
-        <v>86.59999999999999</v>
+      <c r="L36" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="N36" s="8" t="n">
-        <v>17.4</v>
+      <c r="N36" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>91</v>
@@ -3461,20 +3455,20 @@
       <c r="P36" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q36" s="8" t="n">
-        <v>88.09999999999999</v>
+      <c r="Q36" s="3" t="n">
+        <v>24.2</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>52.1</v>
+        <v>55.1</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>11.2</v>
+        <v>13.2</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>18.4</v>
@@ -3482,14 +3476,14 @@
       <c r="W36" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="X36" s="8" t="n">
-        <v>66.59999999999999</v>
+      <c r="X36" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3505,7 +3499,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2192.8</v>
+        <v>192.8</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>119.1</v>
@@ -3521,25 +3515,23 @@
       </c>
       <c r="H37" s="3" t="inlineStr"/>
       <c r="I37" s="3" t="n">
-        <v>110.6</v>
+        <v>10.6</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>75.7</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>711.2</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>71.59999999999999</v>
-      </c>
+        <v>2.7</v>
+      </c>
+      <c r="N37" s="3" t="inlineStr"/>
       <c r="O37" s="3" t="n">
-        <v>4420.3</v>
+        <v>449</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>8.800000000000001</v>
@@ -3548,16 +3540,16 @@
         <v>113.4</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>84.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>313.4</v>
+        <v>13.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>234.8</v>
+        <v>54.8</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>91</v>
@@ -3566,10 +3558,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>409.8</v>
+        <v>9.5</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>88.40000000000001</v>
@@ -3588,7 +3580,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>43.8</v>
+        <v>438.6</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>23.8</v>
@@ -3603,10 +3595,10 @@
         <v>10.8</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>12.3</v>
+        <v>22.3</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>12.1</v>
+        <v>2.1</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.5</v>
@@ -3619,10 +3611,10 @@
         <v>14</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>15.2</v>
+        <v>15.5</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>1.8</v>
@@ -3637,7 +3629,7 @@
         <v>17</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>82.7</v>
+        <v>62.7</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>11</v>
@@ -3671,10 +3663,10 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>39595.3</v>
+        <v>595.3</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>24.2</v>
+        <v>24.5</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>13</v>
@@ -3688,9 +3680,7 @@
       <c r="H39" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="I39" s="3" t="n">
-        <v>13</v>
-      </c>
+      <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="3" t="n">
         <v>0</v>
@@ -3698,8 +3688,8 @@
       <c r="L39" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="M39" s="8" t="n">
-        <v>11.5</v>
+      <c r="M39" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>1.6</v>
@@ -3716,8 +3706,8 @@
       <c r="R39" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="S39" s="8" t="n">
-        <v>20.9</v>
+      <c r="S39" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>52</v>
@@ -3727,9 +3717,9 @@
       </c>
       <c r="V39" s="3" t="inlineStr"/>
       <c r="W39" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="X39" s="8" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X39" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="Y39" s="3" t="n">
@@ -3755,10 +3745,10 @@
         <v>545.4</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>29.3</v>
+        <v>24.3</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>12.8</v>
+        <v>13.8</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>19.1</v>
@@ -3776,16 +3766,16 @@
         <v>4.7</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="M40" s="8" t="n">
-        <v>19</v>
+      <c r="M40" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>1</v>
+        <v>10.7</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>89</v>
@@ -3800,10 +3790,10 @@
         <v>17.9</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>58.8</v>
+        <v>58.5</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>12</v>
@@ -3811,17 +3801,17 @@
       <c r="V40" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="W40" s="8" t="n">
+      <c r="W40" s="3" t="n">
         <v>16</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>1.6</v>
+        <v>16</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>408.4</v>
+        <v>6.2</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3837,13 +3827,13 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>340.1</v>
-      </c>
-      <c r="D41" s="8" t="n">
+        <v>408.4</v>
+      </c>
+      <c r="D41" s="3" t="n">
         <v>23.7</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>18.1</v>
@@ -3851,11 +3841,11 @@
       <c r="G41" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="H41" s="8" t="n">
+      <c r="H41" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>4</v>
@@ -3867,7 +3857,7 @@
         <v>14.8</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15.6</v>
+        <v>13.6</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>19.2</v>
@@ -3884,29 +3874,29 @@
       <c r="R41" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="S41" s="8" t="n">
-        <v>18</v>
+      <c r="S41" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62.2</v>
+        <v>62.5</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>19</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>14.6</v>
+        <v>18.2</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>113.8</v>
+        <v>82</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>19.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3922,22 +3912,22 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>331</v>
+        <v>340.1</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>22.9</v>
+        <v>22.4</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>11.8</v>
+        <v>13.7</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>1.7</v>
@@ -3946,19 +3936,19 @@
         <v>3</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>16.2</v>
+        <v>14.6</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>15.1</v>
+        <v>13.2</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>16.1</v>
+        <v>19.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>2</v>
@@ -3979,19 +3969,19 @@
         <v>10.4</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>20.4</v>
+        <v>18.2</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>12.1</v>
+        <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>18.1</v>
+        <v>22.4</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>110.1</v>
+        <v>28</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>58</v>
+        <v>2.6</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4007,46 +3997,46 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>557.1</v>
+        <v>537</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>13.4</v>
+        <v>23.2</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>1.2</v>
+        <v>13.1</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>99.59999999999999</v>
+        <v>10.1</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>28.8</v>
+        <v>2.5</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="M43" s="8" t="n">
-        <v>35.4</v>
+        <v>16.2</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>15.1</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>1.9</v>
+        <v>16.9</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>22.2</v>
@@ -4055,28 +4045,28 @@
         <v>16.5</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>12.6</v>
+        <v>15.6</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>186.7</v>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v>19.4</v>
+        <v>58</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>11.2</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="W43" s="8" t="n">
-        <v>22.6</v>
+        <v>18.2</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>0</v>
+        <v>557.1</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4092,76 +4082,74 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>2983</v>
-      </c>
-      <c r="D44" s="8" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>91.09999999999999</v>
+        <v>22.1</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>62</v>
+        <v>10.8</v>
       </c>
       <c r="H44" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="U44" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="I44" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L44" s="8" t="n">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="M44" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="P44" s="8" t="n">
-        <v>340.9</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="R44" s="8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="T44" s="3" t="n">
-        <v>351</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>69</v>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v>111.5</v>
+      <c r="V44" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>95.5</v>
+        <v>14.5</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>466.8</v>
+        <v>13.6</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>28.1</v>
+        <v>14.8</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4177,28 +4165,28 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>497</v>
+        <v>2983</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>23.6</v>
+        <v>141.7</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>13.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>18.4</v>
+        <v>10.5</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>10.3</v>
+        <v>62</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>11.8</v>
+        <v>70.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>2.5</v>
+        <v>15.2</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>14.4</v>
+        <v>26.2</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>0.1</v>
@@ -4207,46 +4195,46 @@
         <v>89.40000000000001</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>0.6</v>
+        <v>83</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>15.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>10.1</v>
+        <v>540.9</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>0.8</v>
+        <v>10.6</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>922.8</v>
+        <v>12.7</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>17.1</v>
+        <v>102.4</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>16.2</v>
+        <v>97.5</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>58.5</v>
+        <v>351</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>11.5</v>
+        <v>69</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>118.6</v>
+        <v>111.5</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>15.9</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>16.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>82.8</v>
+        <v>468.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>44.8</v>
+        <v>28.7</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4265,37 +4253,37 @@
         <v>497</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.1</v>
+        <v>23.6</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0.1</v>
+        <v>13.3</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.1</v>
+        <v>18.4</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>145.9</v>
+        <v>19.3</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1.7</v>
+        <v>11.8</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>6.9</v>
+        <v>2.5</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="N46" s="8" t="n">
-        <v>12</v>
+        <v>20.4</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>15.2</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>90.09999999999999</v>
@@ -4304,34 +4292,34 @@
         <v>1.8</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>2.2</v>
+        <v>22.8</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>1.8</v>
+        <v>17.1</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>1</v>
+        <v>16.2</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>11.8</v>
+        <v>58.5</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>1414</v>
+        <v>11.5</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>117.5</v>
-      </c>
-      <c r="W46" s="8" t="n">
-        <v>11151.1</v>
+        <v>18.6</v>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>0.8</v>
+        <v>55.4</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>15.1</v>
+        <v>11.4</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_decimal_place_correction.xlsx
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>58.5</v>
+        <v>585.3</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>25.1</v>
@@ -772,7 +772,7 @@
         <v>14.5</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>2.2</v>
@@ -816,7 +816,7 @@
         <v>388.3</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>14.2</v>
@@ -825,7 +825,7 @@
         <v>19.1</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>2.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>12.3</v>
@@ -934,7 +934,7 @@
         <v>15.9</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>1.2</v>
@@ -946,7 +946,7 @@
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.7</v>
+        <v>17.3</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>18.5</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>22.9</v>
+        <v>229.6</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>21.5</v>
@@ -1001,25 +1001,25 @@
         <v>12.9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>29.9</v>
+        <v>27.2</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>40.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>22.4</v>
+        <v>22.9</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.8</v>
@@ -1049,7 +1049,7 @@
         <v>76</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>5.8</v>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>22.2</v>
+        <v>2224.9</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>118.5</v>
@@ -1098,10 +1098,10 @@
         <v>73.40000000000001</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>60.2</v>
+        <v>60.1</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>166.4</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>59</v>
@@ -1119,7 +1119,7 @@
         <v>86.2</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>12.6</v>
+        <v>312.6</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>53</v>
@@ -1171,7 +1171,7 @@
         <v>12.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>229.5</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>3.3</v>
@@ -1186,7 +1186,7 @@
         <v>13.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>166.4</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>21.8</v>
@@ -1204,10 +1204,10 @@
         <v>17.2</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>21.5</v>
+        <v>62.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>94</v>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>45</v>
+        <v>145.5</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>23.7</v>
@@ -1265,7 +1265,7 @@
         <v>3.3</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>14.7</v>
@@ -1289,7 +1289,7 @@
         <v>17.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>21.5</v>
+        <v>62.5</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>10.6</v>
@@ -1347,16 +1347,16 @@
         <v>0.7</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1</v>
+        <v>10.2</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>1.5</v>
+        <v>15.3</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>14</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>17.2</v>
+        <v>19.2</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>88</v>
@@ -1374,7 +1374,7 @@
         <v>19</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>212.4</v>
+        <v>22.6</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>55.1</v>
@@ -1431,10 +1431,10 @@
         <v>13.5</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>15.9</v>
+        <v>17</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.2</v>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="W12" s="3" t="inlineStr"/>
       <c r="X12" s="3" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>940.5</v>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>32.4</v>
+        <v>324</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>21.8</v>
@@ -1633,7 +1633,7 @@
         <v>92</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>15.5</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.6</v>
@@ -1703,7 +1703,7 @@
         <v>73</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>18.2</v>
@@ -1734,10 +1734,10 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>147.5</v>
+        <v>1475.2</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.8</v>
+        <v>114.8</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>674.7</v>
@@ -1758,7 +1758,7 @@
         <v>6.9</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>46.5</v>
+        <v>46.3</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>73.2</v>
@@ -1767,10 +1767,10 @@
         <v>634.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>12.4</v>
+        <v>712.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6</v>
@@ -1779,7 +1779,7 @@
         <v>96.5</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>83.5</v>
+        <v>83.2</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>88.09999999999999</v>
@@ -1788,7 +1788,7 @@
         <v>394.5</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>24.8</v>
+        <v>24.2</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>84.3</v>
@@ -1800,7 +1800,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>158.8</v>
+        <v>450.2</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>29.5</v>
+        <v>295</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>12.5</v>
+        <v>18.6</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>12.1</v>
+        <v>18.9</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>9.5</v>
@@ -1840,10 +1840,10 @@
         <v>1.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>121.4</v>
+        <v>1.4</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>22.2</v>
+        <v>10.2</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>14.6</v>
@@ -1852,10 +1852,10 @@
         <v>13.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>15.2</v>
+        <v>2.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>15.8</v>
+        <v>15.4</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>1.2</v>
@@ -1956,7 +1956,7 @@
         <v>69.09999999999999</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>18.5</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>40.6</v>
+        <v>440.6</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>25</v>
@@ -1999,7 +1999,7 @@
         <v>19.5</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>12.1</v>
@@ -2026,7 +2026,7 @@
         <v>92</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>24.9</v>
@@ -2075,7 +2075,7 @@
         <v>153.1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>20.7</v>
+        <v>20</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>13.8</v>
@@ -2084,7 +2084,7 @@
         <v>17.3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>8.9</v>
+        <v>19.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>13.8</v>
@@ -2093,7 +2093,7 @@
         <v>1.3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>5.6</v>
@@ -2105,7 +2105,7 @@
         <v>45.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>17.8</v>
+        <v>14.8</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
@@ -2126,7 +2126,7 @@
         <v>76.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>5.7</v>
+        <v>2.2</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>17.6</v>
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>251.7</v>
+        <v>261.7</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>21.9</v>
@@ -2190,7 +2190,7 @@
         <v>15.2</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1.6</v>
+        <v>16.2</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>90.8</v>
@@ -2269,13 +2269,13 @@
         <v>3</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.1</v>
+        <v>16.1</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>91</v>
@@ -2336,13 +2336,13 @@
         <v>69.40000000000001</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>92.5</v>
+        <v>91.2</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>43.7</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>61.2</v>
+        <v>61.3</v>
       </c>
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="n">
@@ -2373,7 +2373,7 @@
         <v>88.8</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>90.5</v>
+        <v>90.3</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>347.9</v>
@@ -2382,7 +2382,7 @@
         <v>40.6</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>91.3</v>
+        <v>22.8</v>
       </c>
       <c r="W23" s="3" t="n">
         <v>81.09999999999999</v>
@@ -2391,7 +2391,7 @@
         <v>9</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>35.5</v>
+        <v>435.5</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>13.8</v>
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>29.5</v>
+        <v>295.4</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>22.6</v>
@@ -2425,7 +2425,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>22.9</v>
+        <v>12.9</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>1.5</v>
@@ -2434,7 +2434,7 @@
         <v>1.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>15.2</v>
@@ -2443,10 +2443,10 @@
         <v>14.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.4</v>
+        <v>16</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>22.1</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>1.4</v>
@@ -2528,7 +2528,7 @@
         <v>14.2</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>1.5</v>
+        <v>15.7</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>91.5</v>
@@ -2602,7 +2602,7 @@
         <v>1.5</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>14.6</v>
@@ -2611,7 +2611,7 @@
         <v>14.1</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.5</v>
+        <v>15.8</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>95</v>
@@ -2623,7 +2623,7 @@
         <v>20.7</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>17.8</v>
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>288.8</v>
+        <v>287.8</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>23.5</v>
@@ -2755,13 +2755,13 @@
         <v>13.8</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>17.9</v>
+        <v>17</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>8</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>23.8</v>
+        <v>13.8</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.9</v>
@@ -2846,7 +2846,7 @@
         <v>8.1</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>13.8</v>
+        <v>33.8</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1.3</v>
@@ -2855,7 +2855,7 @@
         <v>2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>14.9</v>
@@ -2864,7 +2864,7 @@
         <v>14.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>14.1</v>
+        <v>21.2</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>95</v>
@@ -2873,7 +2873,7 @@
         <v>0.8</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>17.8</v>
@@ -2945,7 +2945,7 @@
         <v>71.7</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>79.8</v>
+        <v>79.2</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>0.5</v>
@@ -2963,13 +2963,13 @@
         <v>90.09999999999999</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>361.9</v>
+        <v>361.2</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>34.6</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>88.8</v>
+        <v>87.8</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>81.09999999999999</v>
@@ -3026,10 +3026,10 @@
         <v>14.3</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>16.8</v>
+        <v>16</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>1</v>
@@ -3041,10 +3041,10 @@
         <v>17.5</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>18.1</v>
+        <v>181.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>79.8</v>
+        <v>72.3</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>6.9</v>
@@ -3062,7 +3062,7 @@
         <v>19.8</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>24.4</v>
+        <v>10.4</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>105.1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.2</v>
+        <v>11.2</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>83</v>
@@ -3124,13 +3124,13 @@
         <v>15.8</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>90</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="V32" s="3" t="n">
         <v>15.9</v>
@@ -3145,7 +3145,7 @@
         <v>97</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>482.8</v>
+        <v>1482.8</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>24.2</v>
@@ -3176,7 +3176,7 @@
         <v>11.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>20.6</v>
+        <v>26.6</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>2.6</v>
@@ -3185,7 +3185,7 @@
         <v>4.9</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>13.7</v>
@@ -3194,7 +3194,7 @@
         <v>13</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>1.4</v>
+        <v>14</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>93</v>
@@ -3261,7 +3261,7 @@
         <v>12.6</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>2.3</v>
@@ -3309,7 +3309,7 @@
         <v>15.8</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="Y34" s="3" t="n">
         <v>81</v>
@@ -3362,10 +3362,10 @@
         <v>15.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>11.6</v>
+        <v>17.6</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>2</v>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>498.9</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>24.2</v>
@@ -3423,7 +3423,7 @@
         <v>13.9</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>12.1</v>
+        <v>19.1</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>10.3</v>
@@ -3447,7 +3447,7 @@
         <v>15.6</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>18.2</v>
+        <v>17.2</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>91</v>
@@ -3480,10 +3480,10 @@
         <v>16.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>79.8</v>
+        <v>79</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>192.8</v>
+        <v>2192.8</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>119.1</v>
@@ -3546,7 +3546,7 @@
         <v>84.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>13.4</v>
+        <v>313.4</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>54.8</v>
@@ -3558,10 +3558,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>85.5</v>
+        <v>85.3</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>9.5</v>
+        <v>409.2</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>88.40000000000001</v>
@@ -3586,16 +3586,16 @@
         <v>23.8</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>22.3</v>
+        <v>12.3</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>2.1</v>
@@ -3611,10 +3611,10 @@
         <v>14</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>11.8</v>
+        <v>0.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>15.5</v>
+        <v>15.2</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>1.8</v>
@@ -3680,16 +3680,18 @@
       <c r="H39" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="I39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>16.1</v>
+        <v>28.8</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>1.6</v>
@@ -3745,7 +3747,7 @@
         <v>545.4</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>13.8</v>
@@ -3754,7 +3756,7 @@
         <v>19.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>10.7</v>
+        <v>22.6</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>11.5</v>
@@ -3775,7 +3777,7 @@
         <v>15</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>10.7</v>
+        <v>10.1</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>89</v>
@@ -3805,7 +3807,7 @@
         <v>16</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>82</v>
@@ -3833,7 +3835,7 @@
         <v>23.7</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>18.1</v>
@@ -3881,13 +3883,13 @@
         <v>62.5</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>19</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>18.2</v>
@@ -3918,7 +3920,7 @@
         <v>22.4</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>1.4</v>
+        <v>14.1</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>18.5</v>
@@ -3942,7 +3944,7 @@
         <v>14.6</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>13.2</v>
+        <v>22.6</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>19.2</v>
@@ -3975,10 +3977,10 @@
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>22.4</v>
+        <v>18.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="Z42" s="3" t="n">
         <v>2.6</v>
@@ -4030,7 +4032,7 @@
         <v>15.1</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>16.9</v>
+        <v>16.2</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>92</v>
@@ -4054,10 +4056,10 @@
         <v>11.2</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>18.2</v>
+        <v>17.2</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>15.8</v>
+        <v>15.2</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>4.2</v>
@@ -4082,7 +4084,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>22.1</v>
+        <v>237.1</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>23.4</v>
@@ -4115,7 +4117,7 @@
         <v>13.4</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>11.4</v>
+        <v>19.2</v>
       </c>
       <c r="O44" s="3" t="n">
         <v>91</v>
@@ -4128,7 +4130,7 @@
         <v>16.7</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>15.9</v>
+        <v>16.9</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>59.5</v>
@@ -4171,7 +4173,7 @@
         <v>141.7</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>97.09999999999999</v>
+        <v>797.1</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>10.5</v>
@@ -4198,7 +4200,7 @@
         <v>83</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>540.9</v>
@@ -4207,7 +4209,7 @@
         <v>10.6</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>12.7</v>
+        <v>13.7</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>102.4</v>
@@ -4225,13 +4227,13 @@
         <v>111.5</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>22.2</v>
       </c>
       <c r="X45" s="3" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>468.8</v>
+        <v>466.8</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>28.7</v>
@@ -4262,7 +4264,7 @@
         <v>18.4</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>19.3</v>
+        <v>10.3</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>11.8</v>
@@ -4274,13 +4276,13 @@
         <v>4.4</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>20.4</v>
+        <v>8</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>15.2</v>
@@ -4313,10 +4315,10 @@
         <v>15.9</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>55.4</v>
+        <v>11.4</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>11.4</v>

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_decimal_place_correction.xlsx
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>585.3</v>
+        <v>58.5</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>25.1</v>
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>388.3</v>
+        <v>38.8</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>23.9</v>
@@ -840,13 +840,13 @@
         <v>15.7</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>0</v>
@@ -931,10 +931,10 @@
         <v>13.6</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>15.9</v>
+        <v>1.5</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>22</v>
+        <v>22.4</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>1.2</v>
@@ -946,7 +946,7 @@
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>17.3</v>
+        <v>1.7</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>18.5</v>
@@ -1001,7 +1001,7 @@
         <v>12.9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>1.8</v>
@@ -1019,7 +1019,7 @@
         <v>40.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>22.9</v>
+        <v>20</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.8</v>
@@ -1049,7 +1049,7 @@
         <v>76</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>5.8</v>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2224.9</v>
+        <v>222.9</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>118.5</v>
@@ -1098,10 +1098,10 @@
         <v>73.40000000000001</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>60.1</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>166.4</v>
+        <v>16.4</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>59</v>
@@ -1171,7 +1171,7 @@
         <v>12.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>229.5</v>
+        <v>22.5</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>3.3</v>
@@ -1186,7 +1186,7 @@
         <v>13.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>166.4</v>
+        <v>16.4</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>21.8</v>
@@ -1207,7 +1207,7 @@
         <v>62.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>94</v>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>145.5</v>
+        <v>145</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>23.7</v>
@@ -1253,10 +1253,10 @@
         <v>10.2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.2</v>
+        <v>21.2</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>6.2</v>
+        <v>0.2</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>21.3</v>
@@ -1265,7 +1265,7 @@
         <v>3.3</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>14.7</v>
@@ -1347,7 +1347,7 @@
         <v>0.7</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>15.3</v>
@@ -1356,7 +1356,7 @@
         <v>14</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>88</v>
@@ -1374,7 +1374,7 @@
         <v>19</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>22.6</v>
+        <v>2</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>55.1</v>
@@ -1431,7 +1431,7 @@
         <v>13.5</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>92</v>
@@ -1600,7 +1600,7 @@
         <v>15.4</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>94</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>1</v>
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1475.2</v>
+        <v>147.5</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>114.8</v>
@@ -1743,7 +1743,7 @@
         <v>674.7</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>92.2</v>
+        <v>91.2</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>47.4</v>
@@ -1767,7 +1767,7 @@
         <v>634.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>712.4</v>
+        <v>12.4</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>14.5</v>
@@ -1779,7 +1779,7 @@
         <v>96.5</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>83.2</v>
+        <v>83.5</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>88.09999999999999</v>
@@ -1788,7 +1788,7 @@
         <v>394.5</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>24.2</v>
+        <v>24.8</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>84.3</v>
@@ -1800,7 +1800,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>450.2</v>
+        <v>450</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1822,10 +1822,10 @@
         <v>295</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>18.6</v>
+        <v>13.6</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>18.9</v>
@@ -1843,7 +1843,7 @@
         <v>1.4</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>10.2</v>
+        <v>20.2</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>14.6</v>
@@ -1852,10 +1852,10 @@
         <v>13.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>1.2</v>
@@ -1956,7 +1956,7 @@
         <v>69.09999999999999</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>18.5</v>
@@ -1999,7 +1999,7 @@
         <v>19.5</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>12.1</v>
@@ -2026,7 +2026,7 @@
         <v>92</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>24.9</v>
@@ -2075,7 +2075,7 @@
         <v>153.1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>20</v>
+        <v>20.7</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>13.8</v>
@@ -2084,7 +2084,7 @@
         <v>17.3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>19.9</v>
+        <v>0.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>13.8</v>
@@ -2105,7 +2105,7 @@
         <v>45.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>14.8</v>
+        <v>17.8</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
@@ -2126,7 +2126,7 @@
         <v>76.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>17.6</v>
@@ -2190,7 +2190,7 @@
         <v>15.2</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>16.2</v>
+        <v>16.8</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>90.8</v>
@@ -2269,13 +2269,13 @@
         <v>3</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>16.1</v>
+        <v>16.5</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>91</v>
@@ -2336,17 +2336,17 @@
         <v>69.40000000000001</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>91.2</v>
+        <v>91.3</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>43.7</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>61.3</v>
+        <v>64.3</v>
       </c>
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>0.3</v>
@@ -2382,7 +2382,7 @@
         <v>40.6</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>22.8</v>
+        <v>91.3</v>
       </c>
       <c r="W23" s="3" t="n">
         <v>81.09999999999999</v>
@@ -2443,10 +2443,10 @@
         <v>14.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>1.4</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>400.4</v>
+        <v>40</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>22.6</v>
@@ -2694,7 +2694,7 @@
         <v>14.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>16.8</v>
+        <v>11.8</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>94</v>
@@ -2755,13 +2755,13 @@
         <v>13.8</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>17</v>
+        <v>17.9</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>8</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>13.8</v>
+        <v>83.8</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.9</v>
@@ -2812,7 +2812,7 @@
         <v>15.8</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>83</v>
+        <v>83.8</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>3.2</v>
@@ -2864,7 +2864,7 @@
         <v>14.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>21.2</v>
+        <v>1.6</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>95</v>
@@ -2919,7 +2919,7 @@
         <v>1609.9</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>112.9</v>
+        <v>112.5</v>
       </c>
       <c r="E30" s="3" t="inlineStr"/>
       <c r="F30" s="3" t="n">
@@ -2963,7 +2963,7 @@
         <v>90.09999999999999</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>361.2</v>
+        <v>36.1</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>34.6</v>
@@ -3026,7 +3026,7 @@
         <v>14.3</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>16</v>
@@ -3041,7 +3041,7 @@
         <v>17.5</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>181.1</v>
+        <v>181.2</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>72.3</v>
@@ -3062,7 +3062,7 @@
         <v>19.8</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>10.4</v>
+        <v>2.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>105.1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>11.2</v>
+        <v>1.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>83</v>
@@ -3130,7 +3130,7 @@
         <v>90</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="V32" s="3" t="n">
         <v>15.9</v>
@@ -3145,7 +3145,7 @@
         <v>97</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1482.8</v>
+        <v>482.8</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>24.2</v>
@@ -3176,7 +3176,7 @@
         <v>11.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>26.6</v>
+        <v>28.6</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>2.6</v>
@@ -3194,7 +3194,7 @@
         <v>13</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>14</v>
+        <v>1.4</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>93</v>
@@ -3279,7 +3279,7 @@
         <v>19.6</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>13.1</v>
+        <v>1.3</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>92</v>
@@ -3338,7 +3338,7 @@
         <v>13.6</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>19.3</v>
+        <v>13.3</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>11.4</v>
@@ -3362,7 +3362,7 @@
         <v>15.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>17.6</v>
+        <v>1.7</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>90</v>
@@ -3377,7 +3377,7 @@
         <v>18.8</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>60</v>
@@ -3483,7 +3483,7 @@
         <v>79</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>85.3</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>409.2</v>
+        <v>409</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>88.40000000000001</v>
@@ -3592,7 +3592,7 @@
         <v>18.5</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>12.3</v>
@@ -3680,21 +3680,19 @@
       <c r="H39" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="I39" s="3" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>28.8</v>
+        <v>16</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>1.6</v>
+        <v>30.1</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>94</v>
@@ -3756,7 +3754,7 @@
         <v>19.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>22.6</v>
+        <v>10.7</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>11.5</v>
@@ -3777,7 +3775,7 @@
         <v>15</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>10.1</v>
+        <v>1</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>89</v>
@@ -3807,10 +3805,10 @@
         <v>16</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>6.2</v>
@@ -3835,7 +3833,7 @@
         <v>23.7</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>18.1</v>
@@ -3862,7 +3860,7 @@
         <v>13.6</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>19.2</v>
+        <v>19.8</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>88.90000000000001</v>
@@ -3889,7 +3887,7 @@
         <v>19</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>17</v>
+        <v>17.8</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>18.2</v>
@@ -3944,7 +3942,7 @@
         <v>14.6</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>22.6</v>
+        <v>13.3</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>19.2</v>
@@ -3980,7 +3978,7 @@
         <v>18.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Z42" s="3" t="n">
         <v>2.6</v>
@@ -4084,7 +4082,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>237.1</v>
+        <v>2</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>23.4</v>
@@ -4117,7 +4115,7 @@
         <v>13.4</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>19.2</v>
+        <v>1.4</v>
       </c>
       <c r="O44" s="3" t="n">
         <v>91</v>
@@ -4130,7 +4128,7 @@
         <v>16.7</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>16.9</v>
+        <v>15.9</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>59.5</v>
@@ -4167,7 +4165,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2983</v>
+        <v>298</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>141.7</v>
@@ -4227,7 +4225,7 @@
         <v>111.5</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>22.2</v>
+        <v>95.5</v>
       </c>
       <c r="X45" s="3" t="n">
         <v>99.59999999999999</v>
@@ -4276,13 +4274,13 @@
         <v>4.4</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>15.2</v>
@@ -4315,13 +4313,13 @@
         <v>15.9</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="Y46" s="3" t="n">
         <v>19</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
